--- a/output/第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx
+++ b/output/第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx
@@ -12,8 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_水準の突合" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_伸び率の突合" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_補正の適用と影響" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_町別の受け皿と必要なデータ" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_判定ルールとレッドチーム" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_町別の突合と補正方向" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_住民基本台帳の原表" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_判定ルールとレッドチーム" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -63,7 +64,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -88,6 +89,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -166,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,10 +229,22 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -594,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -681,60 +699,74 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>同じ11年で、住民基本台帳は年+1.54％、社人研は年+1.94％で、社人研が年+0.39ポイント速い。11年の累積では+5.1ポイント（住基＋18.4％に対し社人研＋23.5％）である。令和8年度から令和11年度までの3年に当てはめると、75歳以上を1.15％下方に補正することになる。</t>
+          <t>同じ11年で、住民基本台帳は年+1.54％、社人研は年+1.94％で、社人研が年+0.39ポイント速い。11年の累積では+5.1ポイント（住基＋18.4％に対し社人研＋23.5％）である。令和8年度から令和11年度までの3年に当てはめると、75歳以上を1.15％下方に補正することになる（案A）。ただしこの期間は社人研側の令和2年までが国勢調査の実績であり、推計の当否を検証していない。⑥の案Bを採る。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>⑤ 補正の影響は小さい</t>
+          <t>⑤ 補正の影響は
+　　認定者数では小さい</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>75歳以上を1.15％下方に補正すると、令和11年度の認定者数は2,004人から1,983人へ22人（1.1％）減る。第1号被保険者数も0.7％減るため、保険料基準額への影響は月額22円程度（6,238円→約6,216円）にとどまる。</t>
+          <t>採用する案B（推計期間ベース）で補正すると、令和11年度の第1号被保険者数は9,072人から9,159人へ+87人増え、認定者数は2,004人から1,996人へ-8人となる。増えるのが認定率の低い65〜74歳、減るのが認定率の高い75歳以上であるため、認定者数はほぼ変わらない。保険料基準額は分母が増える分だけ下がり、月額6,238円から約6,153円（-85円）となる。なお案A（実績期間ベース）では認定者数1,983人・保険料約6,216円である。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>⑥ 町別の補正は
-　　まだ確定できない</t>
+          <t>⑥ 突合の期間は
+　　推計期間に改めた</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>3町の総人口の乖離は東川町＋513人・美瑛町＋444人・東神楽町▲408人と向きが異なる。65歳以上・75歳以上でも町ごとに向きが異なる可能性がある。町別の判断には、住民基本台帳の年齢5歳階級別の年次推移（令和2年〜令和8年・町別）が必要である。05シートに社人研側の受け皿を用意した。</t>
+          <t>住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）を受領したため、令和2年から令和7年までの5年で突合を行った。この5年は、社人研 令和5年推計の基準年から最初の推計年までの区間であり、推計そのものを実績で検証している。3町計では、65〜74歳を3年で+3.8％上方に、75歳以上を0.7％下方に補正することになる。社人研は前期高齢者の減少を実績より速く見込んでいる（年1.20ポイント）。これは④の11年ベースの整理では見えていなかった向きである。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>⑦ 総合戦略の目標人口は
+          <t>⑦ 町別の補正方向は
+　　3町で異なる</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>75歳以上は、東川町が上方（3年で+3.2％）、美瑛町が補正しない、東神楽町が下方（4.2％）である。65〜74歳は、東川町が補正しない、美瑛町が上方（+6.2％）、東神楽町が上方（+4.2％）である。3町計で75歳以上に下方補正が生じる原因は、実質的に東神楽町にある。町別の補正係数は算定したが、適用には町別の基準人口（第1号被保険者数・年齢階級別・令和8年3月末）を要するため保留とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>⑧ 総合戦略の目標人口は
 　　伸び率の補正には使わない</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>総合戦略の目標人口は総人口であり、年齢構成を伴わない。65歳以上・75歳以上の伸び率の補正には用いられない。総合戦略は、総人口の水準の妥当性を確かめる材料及び第2章第1節の記述として用いる。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>注1）本表の突合は3町計である。町別は住民基本台帳の年齢5歳階級別の年次推移の受領後に行う。注2）住民基本台帳の値は2つの出所を用いている。平成24年〜令和5年は素案 第2章第1節（各年10月1日現在）、令和8年は別途整理（令和8年1月1日現在）である。時点の定義が異なるため、伸び率の算定には前者のみを用いた。注3）保険料への影響は、給付費が認定者数に比例し、サービスの構成が変わらないと仮定した概算である。第3段階（給付費・保険料）の推計は、単価・基金残高・収納率・所得段階別被保険者数の受領後に確定する。</t>
+    <row r="15" ht="65" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>注1）住民基本台帳の値は3つの出所を用いている。①平成24年〜令和5年は素案 第2章第1節（各年10月1日現在・3町計）、②平成31年〜令和7年は総務省「住民基本台帳に基づく人口、人口動態及び世帯数」年齢別人口（市区町村別）【総計】（各年1月1日現在・町別）、③令和8年は別途整理（令和8年1月1日現在・3町計）である。時点の定義が異なるため、伸び率の算定は同一の出所の中で行った。案Aは①、案Bは②による。注2）②の原表は06シートに収録した。注3）保険料への影響は、給付費が認定者数に比例し、サービスの構成が変わらないと仮定した概算である。第3段階（給付費・保険料）の推計は、単価・基金残高・収納率・所得段階別被保険者数の受領後に確定する。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2060,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2426,12 +2458,160 @@
         </is>
       </c>
     </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>【4　案A（実績期間ベース）と案B（推計期間ベース）の比較】</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>案</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>補正の内容</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度
+65歳以上</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度
+認定者数</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>保険料基準額</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>採否</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>補正なし</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>社人研の伸び率をそのまま用いる</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>9,072人</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>2,004人</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>6,238円</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>案A
+実績期間ベース</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>平成24年→令和5年の11年で算定。75歳以上のみ1.15％下方に補正</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>9,006人</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>1,983人</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>約6,216円（-22円）</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>採らない。この期間の社人研値は令和2年までが国勢調査による実績であり、推計の当否を検証していない</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>案B
+推計期間ベース</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>令和2年→令和7年の5年で算定。65〜74歳を+3.77％、75歳以上を0.73％補正</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>9,159人</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>1,996人</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>約6,153円（-85円）</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>★こちらを採る。社人研 令和5年推計の基準年から第1推計年までの区間であり、推計そのものを実績で検証している</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="78" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>注5）案Bを採る理由は3点である。第1に、社人研 令和5年推計は令和2年国勢調査を基準年としており、令和7年は最初の推計年である。令和2年から令和7年までの区間で実績と突き合わせることは、推計そのものの当否を検証することにあたる。案Aの期間（平成24年〜令和5年）は、社人研側の令和2年までが国勢調査による実績であり、推計の検証になっていない（07シートの指摘No.4）。第2に、案Bは65〜74歳と75歳以上を分けて補正する。社人研は前期高齢者の減少を実績より速く見込んでおり（3町計で年1.20ポイント）、75歳以上のみを補正する案Aでは、この向きが取り込まれない。第3に、案Bは補正の対象期間（令和8年度〜令和11年度）に時点が近い。注6）案Bでは65歳以上が+87人となる一方、認定者数は1996人にとどまる。前期高齢者の上方補正は認定率の低い層を増やすためである。保険料基準額は分母（第1号被保険者数）が増えることにより約85円下がる。注7）案Bの補正係数は5年の実績によるものであり、令和8年1月1日現在の値が公表され次第、6年に更新する。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2443,42 +2623,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>町別の突合の受け皿（社人研側）と、必要なデータ</t>
+          <t>町別の突合と、3町それぞれの補正方向</t>
         </is>
       </c>
     </row>
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>町別の補正の判断には、住民基本台帳の年齢5歳階級別の年次推移（町別）が必要である。本シートは社人研側の値を算定し、突合の受け皿とする。</t>
+          <t>住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）の受領により、町別の突合が可能となった。令和2年1月1日から令和7年1月1日までの5年の実績の伸び率と、社人研 令和5年推計の令和2年から令和7年までの伸び率とを町別・年齢階級別に突き合わせ、補正方向を確定する。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>【1　社人研推計による町別の65歳以上（受け皿）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
+          <t>【1　町別・年齢階級別の伸び率の突合（令和2年→令和7年・5年）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>町</t>
@@ -2486,42 +2667,54 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2020年</t>
+          <t>区分</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2025年</t>
+          <t>住民基本台帳
+令和2年</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2030年</t>
+          <t>住民基本台帳
+令和7年</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2035年</t>
+          <t>住基
+年平均</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2040年</t>
+          <t>社人研
+令和2年</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2045年</t>
+          <t>社人研
+令和7年</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>2050年</t>
+          <t>社人研
+年平均</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>算定方法</t>
+          <t>年平均の差
+（社人研－住基）</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>補正方向</t>
         </is>
       </c>
     </row>
@@ -2531,608 +2724,1060 @@
           <t>東川町</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>2,760</t>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>65〜74歳</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>2,702</t>
+          <t>1,279人</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>2,692</t>
+          <t>1,085人</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>2,716</t>
+          <t>-3.24％</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>2,837</t>
+          <t>1,270人</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>2,870</t>
+          <t>1,070人</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>2,842</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>見える化A1の町別総人口×町別高齢化率</t>
+          <t>-3.37％</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>-0.13pt</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>補正しない（3年で+0.4％）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>75歳以上</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>1,418人</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>1,637人</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>+2.91％</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>1,490人</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>1,632人</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>+1.83％</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>-1.08pt</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>上方に補正（3年で+3.2％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="22" t="inlineStr"/>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>65歳以上</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>2,697人</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>2,722人</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>+0.18％</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>2,760人</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>2,702人</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>-0.43％</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>-0.61pt</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>上方に補正（3年で+1.8％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>美瑛町</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>3,751</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>3,504</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>3,329</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>3,170</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>3,090</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>2,904</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>2,698</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>見える化A1の町別総人口×町別高齢化率</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>65〜74歳</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>1,609人</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>1,402人</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>-2.72％</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>1,617人</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>1,274人</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>-4.66％</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>-1.94pt</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>上方に補正（3年で+6.2％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="5" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>75歳以上</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>2,151人</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>2,226人</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>+0.69％</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>2,134人</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>2,230人</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>+0.88％</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>+0.20pt</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>補正しない（3年で-0.6％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="22" t="inlineStr"/>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>65歳以上</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>3,760人</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>3,628人</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>-0.71％</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>3,751人</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>3,504人</t>
+        </is>
+      </c>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>-1.35％</t>
+        </is>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>-0.64pt</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>上方に補正（3年で+2.0％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>東神楽町</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>2,927</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>3,119</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>3,286</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>3,488</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>3,704</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>3,747</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>3,705</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>見える化A1の町別総人口×町別高齢化率</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>65〜74歳</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>1,343人</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>1,330人</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>-0.19％</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>1,384人</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>1,280人</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>-1.55％</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>-1.36pt</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>上方に補正（3年で+4.2％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>75歳以上</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>1,399人</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>1,552人</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>+2.10％</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>1,543人</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>1,839人</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>+3.58％</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>+1.48pt</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>下方に補正（3年で-4.2％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="22" t="inlineStr"/>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>65歳以上</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>2,742人</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>2,882人</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>+1.00％</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>2,927人</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>3,119人</t>
+        </is>
+      </c>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>+1.28％</t>
+        </is>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>+0.28pt</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>下方に補正（3年で-0.8％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>3町計</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>9,438</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>9,325</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>9,307</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>9,374</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>9,632</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>9,521</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>9,246</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>見える化A2と一致（丸めの差を除く）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>見える化A2</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>9,437</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>9,323</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>9,310</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>9,378</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>9,633</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>9,522</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>9,239</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>【2　社人研推計による町別の75歳以上（受け皿・按分値）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>65〜74歳</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>4,231人</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>3,817人</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>-2.04％</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>4,270人</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>3,622人</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>-3.24％</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>-1.20pt</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>上方に補正（3年で+3.8％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="5" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>75歳以上</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>4,968人</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>5,415人</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>+1.74％</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>5,167人</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>5,701人</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>+1.99％</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>+0.25pt</t>
+        </is>
+      </c>
+      <c r="J16" s="18" t="inlineStr">
+        <is>
+          <t>下方に補正（3年で-0.7％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="22" t="inlineStr"/>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>65歳以上</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>9,199人</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>9,232人</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>+0.07％</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>9,437人</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>9,323人</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>-0.24％</t>
+        </is>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>-0.31pt</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>上方に補正（3年で+0.9％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>注1）「65歳以上」の行は「65〜74歳」と「75歳以上」の合計であり、内訳の2区分と重複するため網掛けとした。補正は内訳の2区分に対して行う。注2）補正方向は、年平均の差が±0.20ポイント未満のときは「補正しない」、社人研が速いときは「下方に補正」、住民基本台帳が速いときは「上方に補正」とした（07シートの判定ルール）。美瑛町の75歳以上は差が0.195ポイントで、判定の境界にある。表示は四捨五入して+0.20ポイントとなるが、しきい値0.20ポイントを下回るため「補正しない」とした［要確認］。注3）「3年で〇％」は、令和8年度を起点に令和11年度までの3年に年平均の差を当てはめた累積である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>【2　町別の読み方】</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>町</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>2020年</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>2025年</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>2030年</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>2035年</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>2040年</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>2045年</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>2050年</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>算定方法</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>補正方向の要点</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>背景</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="76" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>東川町</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>1,490</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>1,632</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>1,699</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>1,663</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>1,680</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>1,720</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>1,827</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>令和2年国勢調査の町別75歳以上を起点に、3町計の後期高齢者比の推移で按分した</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>美瑛町</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>2,134</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>2,230</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>2,214</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>2,045</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>1,927</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>1,834</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>1,827</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>令和2年国勢調査の町別75歳以上を起点に、3町計の後期高齢者比の推移で按分した</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>東神楽町</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>1,543</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>1,839</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>2,024</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>2,085</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>2,141</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>2,192</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>2,324</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>令和2年国勢調査の町別75歳以上を起点に、3町計の後期高齢者比の推移で按分した</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>3町計</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>5,167</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>5,701</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>5,937</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>5,793</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>5,748</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>5,746</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr">
-        <is>
-          <t>5,978</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>見える化A3と一致する</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>【3　町別の突合に必要なデータ】</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="4" t="inlineStr"/>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>必要なデータ</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>形式</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>何のために必要か</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="46" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>町別・年齢5歳階級別の住民基本台帳人口（令和2年〜令和8年）</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>各年1月1日又は10月1日現在で統一。0〜4歳から100歳以上までの21階級。総数・日本人・外国人の別。</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n"/>
-      <c r="H21" s="17" t="n"/>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>町別の65歳以上・75歳以上の伸び率を算定し、社人研の伸び率と突き合わせる。これがないと町別の補正方向を確定できない</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="46" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>町別の第1号被保険者数（年齢階級別・令和8年3月末）</t>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>65〜74歳は社人研とほぼ一致する（差-0.13ポイント）。75歳以上は住民基本台帳の方が速く（差-1.08ポイント）、3年で+3.2％の上方補正となる。3町で唯一、75歳以上を上方に補正する町である。</t>
         </is>
       </c>
       <c r="C22" s="16" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>65〜74歳・75〜84歳・85歳以上の3階級。</t>
-        </is>
-      </c>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
       <c r="F22" s="16" t="n"/>
       <c r="G22" s="16" t="n"/>
-      <c r="H22" s="17" t="n"/>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>町別の基準人口を確定する。現在は3町計のみを見える化B4cから得ている</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="46" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>町別の要介護認定者数（要介護度別・令和8年3月末）</t>
+      <c r="H22" s="16" t="n"/>
+      <c r="I22" s="17" t="n"/>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>総人口が令和2年から令和7年にかけて8,380人から8,673人へ293人増えた3町で唯一の町である。社人研は同期間に減少を見込んでいた。移住施策による転入が75歳以上の増加を上回る速度で総人口を押し上げている一方、75歳以上そのものも実績の方が速く増えている</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="76" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>65〜74歳は社人研の減少見込みが実績より大幅に速く（差-1.94ポイント）、3年で+6.2％の上方補正となる。75歳以上は差が+0.20ポイントで補正しない。</t>
         </is>
       </c>
       <c r="C23" s="16" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>要支援1〜要介護5の7区分。</t>
-        </is>
-      </c>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="16" t="n"/>
       <c r="F23" s="16" t="n"/>
       <c r="G23" s="16" t="n"/>
-      <c r="H23" s="17" t="n"/>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>町別の認定率を算定する。現在は3町計のみである。町別の見込量の算定に必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>注1）【2】の町別75歳以上は按分値である。令和2年国勢調査の町別75歳以上（東川町1,490人・美瑛町2,133人・東神楽町1,544人）を起点に、3町計の後期高齢者比の推移を町別の比に同じ倍率で当てはめ、3町計が見える化A3と一致するようスケーリングした。町ごとに後期化の速度が異なる場合は誤差が生じる。注2）令和2年国勢調査の町別65歳以上（2,759・3,749・2,929）と75歳以上（1,490・2,133・1,544）は、いずれも3町計が見える化A2・A3の令和2年値と完全に一致する（9,437人・5,167人）。起点の値は確かである。注3）①は資料提供依頼No.9として最高優先で依頼している。別途、北海道「住民基本台帳年齢階級別人口（市区町村別）」の令和2年〜令和8年分が整理されているため、その共有をお願いしている。</t>
+      <c r="H23" s="16" t="n"/>
+      <c r="I23" s="17" t="n"/>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>3町で最も高齢化率が高く（令和7年39.1％）、総人口の減少も最も速い。社人研は令和2年から令和7年に775人の減少を見込んでいたが、実績は629人の減少にとどまった。前期高齢者が想定ほど減っていないことが乖離の主因である</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="76" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>65〜74歳は3年で+4.2％の上方補正、75歳以上は社人研が年+1.48ポイント速く、3年で4.2％の下方補正となる。3町で唯一、75歳以上を下方に補正する町である。</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="16" t="n"/>
+      <c r="H24" s="16" t="n"/>
+      <c r="I24" s="17" t="n"/>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>3町計で75歳以上に下方補正が生じる原因は、実質的にこの町にある。社人研は令和7年の75歳以上を1,839人と見込んでいたが、実績は1,552人で287人少ない。旭川市に隣接し人口構成が若い町で、後期高齢化の速度が推計より緩やかである</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="76" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>3町計</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>65〜74歳は3年で+3.8％の上方補正、75歳以上は3年で0.7％の下方補正となる。両者を合わせた65歳以上は3年で+0.9％の上方となる。</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="16" t="n"/>
+      <c r="I25" s="17" t="n"/>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>3町計では、前期高齢者の上方補正が後期高齢者の下方補正を上回る。認定率が高いのは後期高齢者であるため、認定者数への影響は65歳以上の増加ほどには大きくならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>【3　町別の補正係数（令和8年度→令和11年度の3年）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>町</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>65〜74歳</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>75歳以上</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>適用の可否</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr"/>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>確認を要する点</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>1.0322</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>適用は保留　←　町別の基準人口が未受領</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="n"/>
+      <c r="H29" s="16" t="n"/>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>社人研側の町別75歳以上は当方の按分値である。町別の公表値ではない</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>1.0624</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>適用は保留　←　町別の基準人口が未受領</t>
+        </is>
+      </c>
+      <c r="G30" s="16" t="n"/>
+      <c r="H30" s="16" t="n"/>
+      <c r="I30" s="17" t="n"/>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>社人研側の町別75歳以上は当方の按分値である。町別の公表値ではない</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>1.0420</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>0.9578</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>適用は保留　←　町別の基準人口が未受領</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="n"/>
+      <c r="H31" s="16" t="n"/>
+      <c r="I31" s="17" t="n"/>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>社人研側の町別75歳以上は当方の按分値である。町別の公表値ではない</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>3町計</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>1.0377</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>0.9927</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>適用できる</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="n"/>
+      <c r="H32" s="16" t="n"/>
+      <c r="I32" s="17" t="n"/>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="65" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>注1）町別の補正係数は算定したが、適用は保留する。当方の推計は基準人口（第1号被保険者数）に伸び率を掛ける構造であるため、町別に適用するには町別の基準人口（65〜74歳・75〜84歳・85歳以上の第1号被保険者数、令和8年3月末）が必要である。現在は3町計のみを見える化B4cから得ている。注2）社人研側の町別75歳以上は、令和2年国勢調査の町別75歳以上を起点に3町計の後期高齢者比の推移で按分した値である。町ごとに後期化の速度が異なる場合は誤差が生じる。町別65歳以上は見える化A1の町別総人口×町別高齢化率であり、按分ではない。したがって、65〜74歳と75歳以上の切り分けには按分の仮定が入っている点に留意を要する［要確認］。注3）補正を町別に適用しない場合でも、サービス見込量の町別配分や施設整備の判断では、東川町と東神楽町で75歳以上の伸びの向きが逆であることを踏まえる必要がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>【4　なお必要なデータ】</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="4" t="inlineStr"/>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>必要なデータ</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr"/>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>何のために必要か</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>町別の第1号被保険者数（年齢階級別・令和8年3月末）</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="16" t="n"/>
+      <c r="G37" s="16" t="n"/>
+      <c r="H37" s="16" t="n"/>
+      <c r="I37" s="17" t="n"/>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>町別の補正を適用するための基準人口。65〜74歳・75〜84歳・85歳以上の3階級。現在は3町計のみである</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>町別の要介護認定者数（要介護度別・令和8年3月末）</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
+      <c r="G38" s="16" t="n"/>
+      <c r="H38" s="16" t="n"/>
+      <c r="I38" s="17" t="n"/>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>町別の認定率を算定する。町別の見込量の算定に必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>住所地特例の適用者数（町別・令和8年3月末）</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="16" t="n"/>
+      <c r="G39" s="16" t="n"/>
+      <c r="H39" s="16" t="n"/>
+      <c r="I39" s="17" t="n"/>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>住民基本台帳人口と第1号被保険者数の差の説明。07シートの指摘No.1の反証条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>令和8年1月1日現在の年齢5歳階級別人口（町別）</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="16" t="n"/>
+      <c r="G40" s="16" t="n"/>
+      <c r="H40" s="16" t="n"/>
+      <c r="I40" s="17" t="n"/>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>本シートは令和7年1月1日までである。令和8年分が公表され次第、6年の伸び率に更新する</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="39" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>出所）総務省「住民基本台帳に基づく人口、人口動態及び世帯数」年齢別人口（市区町村別）【総計】各年1月1日現在。団体コードは東川町014583・美瑛町014591・東神楽町014532。社人研は「日本の地域別将来推計人口（令和5年推計）」により、介護保険事業状況報告等の見える化システムのA1・A2・A3・A4から取得した。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="E22:H22"/>
+  <mergeCells count="28">
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="F30:I30"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A33:J33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3144,7 +3789,2509 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:M48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>住民基本台帳の年齢5歳階級別人口（町別・平成31年〜令和7年）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>05シートの突合に用いた原表である。総務省「住民基本台帳に基づく人口、人口動態及び世帯数」年齢別人口（市区町村別）【総計】各年1月1日現在。日本人住民と外国人住民の合計である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>【東川町】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>年（1月1日）</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>総人口</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>65〜69歳</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>70〜74歳</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>75〜79歳</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>80〜84歳</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>85〜89歳</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>90〜94歳</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>95〜99歳</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>100歳以上</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>65歳以上</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>75歳以上</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>高齢化率</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>平成31年</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>8,382</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>2,699</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>1,410</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>32.2％</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>令和2年</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>8,380</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>2,697</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>1,418</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>32.2％</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>令和3年</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>8,437</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>2,718</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>1,445</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>32.2％</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>令和4年</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>8,390</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>2,718</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>1,476</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>32.4％</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>令和5年</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>8,601</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>2,715</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>1,514</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>31.6％</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>令和6年</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>8,576</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>2,692</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>1,544</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>31.4％</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>令和7年</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>8,673</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>2,722</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>1,637</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>31.4％</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>5年の増減
+（令和2→7年）</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>+293</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>-179</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>+111</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="inlineStr">
+        <is>
+          <t>+54</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t>+26</t>
+        </is>
+      </c>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>+6</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
+        <is>
+          <t>+25</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="K13" s="25" t="inlineStr">
+        <is>
+          <t>+25</t>
+        </is>
+      </c>
+      <c r="L13" s="25" t="inlineStr">
+        <is>
+          <t>+219</t>
+        </is>
+      </c>
+      <c r="M13" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>【美瑛町】</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>年（1月1日）</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>総人口</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>65〜69歳</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>70〜74歳</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>75〜79歳</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>80〜84歳</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>85〜89歳</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>90〜94歳</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>95〜99歳</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>100歳以上</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>65歳以上</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>75歳以上</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>高齢化率</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>平成31年</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>10,043</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>859</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>3,764</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>2,146</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>37.5％</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>令和2年</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>9,912</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>3,760</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>2,151</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>37.9％</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>令和3年</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>9,775</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>3,757</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>2,136</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>38.4％</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>令和4年</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>9,636</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>3,720</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>2,133</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>38.6％</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>令和5年</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>9,573</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>3,696</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>2,158</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>38.6％</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>令和6年</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>9,432</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>3,653</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>2,197</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>38.7％</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>令和7年</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>9,283</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>3,628</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>2,226</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>39.1％</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>5年の増減
+（令和2→7年）</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>-629</t>
+        </is>
+      </c>
+      <c r="C24" s="25" t="inlineStr">
+        <is>
+          <t>-177</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F24" s="25" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="G24" s="25" t="inlineStr">
+        <is>
+          <t>+8</t>
+        </is>
+      </c>
+      <c r="H24" s="25" t="inlineStr">
+        <is>
+          <t>+60</t>
+        </is>
+      </c>
+      <c r="I24" s="25" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="K24" s="25" t="inlineStr">
+        <is>
+          <t>-132</t>
+        </is>
+      </c>
+      <c r="L24" s="25" t="inlineStr">
+        <is>
+          <t>+75</t>
+        </is>
+      </c>
+      <c r="M24" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>【東神楽町】</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>年（1月1日）</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>総人口</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>65〜69歳</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>70〜74歳</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>75〜79歳</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>80〜84歳</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>85〜89歳</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>90〜94歳</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>95〜99歳</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>100歳以上</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>65歳以上</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>75歳以上</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>高齢化率</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>平成31年</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>10,321</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>2,683</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>1,379</t>
+        </is>
+      </c>
+      <c r="M28" s="9" t="inlineStr">
+        <is>
+          <t>26.0％</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>令和2年</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>10,239</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>2,742</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>1,399</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>26.8％</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>令和3年</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>10,154</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>2,776</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>1,397</t>
+        </is>
+      </c>
+      <c r="M30" s="9" t="inlineStr">
+        <is>
+          <t>27.3％</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>令和4年</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>10,110</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>2,823</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>1,433</t>
+        </is>
+      </c>
+      <c r="M31" s="9" t="inlineStr">
+        <is>
+          <t>27.9％</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>令和5年</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>9,945</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>2,834</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>1,430</t>
+        </is>
+      </c>
+      <c r="M32" s="9" t="inlineStr">
+        <is>
+          <t>28.5％</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>令和6年</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>9,862</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>2,846</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>1,492</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>28.9％</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>令和7年</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>9,775</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>2,882</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>1,552</t>
+        </is>
+      </c>
+      <c r="M34" s="9" t="inlineStr">
+        <is>
+          <t>29.5％</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>5年の増減
+（令和2→7年）</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>-464</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="inlineStr">
+        <is>
+          <t>-26</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="inlineStr">
+        <is>
+          <t>+13</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="inlineStr">
+        <is>
+          <t>+90</t>
+        </is>
+      </c>
+      <c r="F35" s="25" t="inlineStr">
+        <is>
+          <t>+27</t>
+        </is>
+      </c>
+      <c r="G35" s="25" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="H35" s="25" t="inlineStr">
+        <is>
+          <t>+26</t>
+        </is>
+      </c>
+      <c r="I35" s="25" t="inlineStr">
+        <is>
+          <t>+12</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="K35" s="25" t="inlineStr">
+        <is>
+          <t>+140</t>
+        </is>
+      </c>
+      <c r="L35" s="25" t="inlineStr">
+        <is>
+          <t>+153</t>
+        </is>
+      </c>
+      <c r="M35" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>【3町計】</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>年（1月1日）</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>総人口</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>65〜69歳</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>70〜74歳</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>75〜79歳</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>80〜84歳</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>85〜89歳</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>90〜94歳</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>95〜99歳</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>100歳以上</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>65歳以上</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>75歳以上</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>高齢化率</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>平成31年</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>28,746</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>2,269</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>1,942</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>1,716</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>1,476</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>1,029</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K39" s="11" t="inlineStr">
+        <is>
+          <t>9,146</t>
+        </is>
+      </c>
+      <c r="L39" s="11" t="inlineStr">
+        <is>
+          <t>4,935</t>
+        </is>
+      </c>
+      <c r="M39" s="11" t="inlineStr">
+        <is>
+          <t>31.8％</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>令和2年</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>28,531</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>2,134</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>2,097</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>1,735</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>1,445</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>1,082</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K40" s="11" t="inlineStr">
+        <is>
+          <t>9,199</t>
+        </is>
+      </c>
+      <c r="L40" s="11" t="inlineStr">
+        <is>
+          <t>4,968</t>
+        </is>
+      </c>
+      <c r="M40" s="11" t="inlineStr">
+        <is>
+          <t>32.2％</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>令和3年</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>28,366</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>2,045</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>2,228</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>1,663</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>1,449</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>1,107</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K41" s="11" t="inlineStr">
+        <is>
+          <t>9,251</t>
+        </is>
+      </c>
+      <c r="L41" s="11" t="inlineStr">
+        <is>
+          <t>4,978</t>
+        </is>
+      </c>
+      <c r="M41" s="11" t="inlineStr">
+        <is>
+          <t>32.6％</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>令和4年</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>28,136</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>1,933</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>2,286</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>1,655</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>1,471</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>1,127</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K42" s="11" t="inlineStr">
+        <is>
+          <t>9,261</t>
+        </is>
+      </c>
+      <c r="L42" s="11" t="inlineStr">
+        <is>
+          <t>5,042</t>
+        </is>
+      </c>
+      <c r="M42" s="11" t="inlineStr">
+        <is>
+          <t>32.9％</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>令和5年</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>28,119</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>1,859</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>2,284</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>1,687</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>1,490</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>1,086</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K43" s="11" t="inlineStr">
+        <is>
+          <t>9,245</t>
+        </is>
+      </c>
+      <c r="L43" s="11" t="inlineStr">
+        <is>
+          <t>5,102</t>
+        </is>
+      </c>
+      <c r="M43" s="11" t="inlineStr">
+        <is>
+          <t>32.9％</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>令和6年</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>27,870</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>1,761</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>2,197</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>1,796</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>1,504</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>1,108</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K44" s="11" t="inlineStr">
+        <is>
+          <t>9,191</t>
+        </is>
+      </c>
+      <c r="L44" s="11" t="inlineStr">
+        <is>
+          <t>5,233</t>
+        </is>
+      </c>
+      <c r="M44" s="11" t="inlineStr">
+        <is>
+          <t>33.0％</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>令和7年</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>27,731</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>1,752</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>2,065</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>1,935</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>1,520</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>1,114</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K45" s="11" t="inlineStr">
+        <is>
+          <t>9,232</t>
+        </is>
+      </c>
+      <c r="L45" s="11" t="inlineStr">
+        <is>
+          <t>5,415</t>
+        </is>
+      </c>
+      <c r="M45" s="11" t="inlineStr">
+        <is>
+          <t>33.3％</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t>5年の増減
+（令和2→7年）</t>
+        </is>
+      </c>
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>-800</t>
+        </is>
+      </c>
+      <c r="C46" s="25" t="inlineStr">
+        <is>
+          <t>-382</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="inlineStr">
+        <is>
+          <t>-32</t>
+        </is>
+      </c>
+      <c r="E46" s="25" t="inlineStr">
+        <is>
+          <t>+200</t>
+        </is>
+      </c>
+      <c r="F46" s="25" t="inlineStr">
+        <is>
+          <t>+75</t>
+        </is>
+      </c>
+      <c r="G46" s="25" t="inlineStr">
+        <is>
+          <t>+32</t>
+        </is>
+      </c>
+      <c r="H46" s="25" t="inlineStr">
+        <is>
+          <t>+92</t>
+        </is>
+      </c>
+      <c r="I46" s="25" t="inlineStr">
+        <is>
+          <t>+51</t>
+        </is>
+      </c>
+      <c r="J46" s="25" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="K46" s="25" t="inlineStr">
+        <is>
+          <t>+33</t>
+        </is>
+      </c>
+      <c r="L46" s="25" t="inlineStr">
+        <is>
+          <t>+447</t>
+        </is>
+      </c>
+      <c r="M46" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="65" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>注1）平成31年は平成31年1月1日現在である。同年5月に改元されたため令和元年1月1日は存在しない。注2）本表は総計（日本人住民＋外国人住民）である。第1号被保険者は外国人住民を含むため、総計を用いた。注3）総人口は0歳から100歳以上までの総数であり、本表に掲げた65歳以上の8階級のほかに64歳以下を含む。注4）国勢調査人口とは定義が異なる。令和2年について、住民基本台帳（令和2年1月1日）は東川町8,380人・美瑛町9,912人・東神楽町10,239人であり、国勢調査（令和2年10月1日）の8,314人・9,668人・10,127人をいずれも上回る。伸び率の突合は同一の出所の中で行っているため、この水準の差は突合の結果に影響しない。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="A26:M26"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A2:M2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3275,7 +6422,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>3年で0.6〜1.5％の差。75歳以上の年0.40ポイントはここに当たる</t>
+          <t>3年で0.6〜1.5％の差。3町計の75歳以上（年0.25ポイント）はここに当たる</t>
         </is>
       </c>
     </row>
@@ -3302,7 +6449,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>3年で1.5％以上の差。社人研の伸び率をそのまま使う前提が成り立たない可能性がある</t>
+          <t>3年で1.5％以上の差。3町計の65〜74歳（年1.20ポイント）と東神楽町の75歳以上（年1.48ポイント）はここに当たる</t>
         </is>
       </c>
     </row>
@@ -3329,102 +6476,102 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>3町計で相殺されて見えなくなることを避ける</t>
+          <t>3町計で相殺されて見えなくなることを避ける。75歳以上は東川町が上方・東神楽町が下方で向きが逆であり、この条件に当たる</t>
         </is>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
+          <t>⑦</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>比較の期間</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>社人研推計の基準年から推計年までの区間が取れる場合</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>その区間を優先する</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>推計そのものの当否を検証できる。基準年より前の区間は、社人研側が国勢調査の実績であり検証にならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t>⑥</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>総合戦略</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>総人口の目標値</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>伸び率の補正には用いない</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>総合戦略の目標人口は年齢構成を伴わない。総人口の水準の妥当性の確認と、第2章第1節の記述に用いる</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>【2　本表への指摘（レッドチーム方式）】</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>指摘</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>根拠</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>反証条件</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="86" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>重大</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>「水準は既に住基ベースだから補正不要」という結論は、第1号被保険者数と住民基本台帳の65歳以上人口を同じものとして扱っている。</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>第1号被保険者には住所地特例の適用者が含まれ、住民基本台帳の65歳以上人口とは一致しない。当方の基準65歳以上9,090人と住民基本台帳9,176人には86人（0.9％）の差がある。</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>住所地特例の適用者数（区域内の施設に入所する区域外の住民、及びその逆）が得られれば、差の説明ができる。説明できれば結論は維持される</t>
         </is>
       </c>
     </row>
     <row r="16" ht="86" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
@@ -3434,141 +6581,223 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>住民基本台帳と社人研の伸び率の差を「社人研が速い」と解したが、この差は推計の精度ではなく統計の差である可能性がある。</t>
+          <t>「水準は既に住基ベースだから補正不要」という結論は、第1号被保険者数と住民基本台帳の65歳以上人口を同じものとして扱っている。</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>社人研の令和5年までの値は国勢調査による実績の補間であり、推計値ではない。国勢調査（常住者）と住民基本台帳（住民登録）の差が11年で拡大しただけであれば、将来の伸び率を補正する根拠にはならない。</t>
+          <t>第1号被保険者には住所地特例の適用者が含まれ、住民基本台帳の65歳以上人口とは一致しない。当方の基準65歳以上9,090人と住民基本台帳9,176人には86人（0.9％）の差がある。</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>国勢調査と住民基本台帳の差の推移（総人口・65歳以上・75歳以上）を算定し、差の拡大が75歳以上に固有かどうかを確かめる。全年齢で一様に拡大していれば、統計の差である</t>
+          <t>住所地特例の適用者数（区域内の施設に入所する区域外の住民、及びその逆）が得られれば、差の説明ができる。説明できれば結論は維持される</t>
         </is>
       </c>
     </row>
     <row r="17" ht="86" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>重大
+【一部解消】</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>補正係数を令和8年度から3年に適用したが、基準年度は令和7年度である。適用する年数が1年ずれている。</t>
+          <t>住民基本台帳と社人研の伸び率の差を「社人研が速い」と解したが、この差は推計の精度ではなく統計の差である可能性がある。</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>推計の基準年度（BASE_Y）は令和7年（2025年）である。令和11年度までは4年であり、3年ではない。</t>
+          <t>社人研の令和5年までの値は国勢調査による実績の補間であり、推計値ではない。国勢調査（常住者）と住民基本台帳（住民登録）の差が11年で拡大しただけであれば、将来の伸び率を補正する根拠にはならない。【一部解消】案B（令和2年→令和7年）では社人研側の令和7年が推計値であるため、推計の当否を検証している。ただし起点の令和2年は国勢調査の実績であり、統計の差が5年で拡大した分は依然として混入する。</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>4年で適用すると補正は1.54％となり、1.15％より大きくなる。どちらを採るかは、基準人口の時点（令和8年3月末＝令和7年度末）をどう扱うかによる</t>
+          <t>国勢調査と住民基本台帳の差の推移（総人口・65歳以上・75歳以上）を算定し、差の拡大が75歳以上に固有かどうかを確かめる。全年齢で一様に拡大していれば、統計の差である。令和7年国勢調査の年齢別集計（令和8年11月頃）が出れば決着する</t>
         </is>
       </c>
     </row>
     <row r="18" ht="86" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>「保険料への影響は月額22円にとどまる」という結論は、給付費が認定者数に比例するという仮定に依存している。</t>
+          <t>補正係数を令和8年度から3年に適用したが、基準年度は令和7年度である。適用する年数が1年ずれている。</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>75歳以上の減は重度者の減であり、1人当たり給付費の高い層が減る。給付費の減は認定者数の減より大きくなる可能性がある。</t>
+          <t>推計の基準年度（BASE_Y）は令和7年（2025年）である。令和11年度までは4年であり、3年ではない。</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>要介護度別の給付費単価を用いて再計算する。第2段階（サービス見込量）の算定チェーンで確認できる</t>
+          <t>4年で適用すると補正は1.54％となり、1.15％より大きくなる。どちらを採るかは、基準人口の時点（令和8年3月末＝令和7年度末）をどう扱うかによる</t>
         </is>
       </c>
     </row>
     <row r="19" ht="86" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>町別75歳以上の按分は、3町の後期化の速度が同じであると仮定している。</t>
+          <t>「保険料への影響は月額22円にとどまる」という結論は、給付費が認定者数に比例するという仮定に依存している。</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>令和2年の75歳以上/65歳以上比は東川町54.0％・美瑛町56.9％・東神楽町52.7％と差がある。この差が将来も同じ倍率で動くという保証はない。</t>
+          <t>75歳以上の減は重度者の減であり、1人当たり給付費の高い層が減る。給付費の減は認定者数の減より大きくなる可能性がある。</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>町別の年齢5歳階級別の住民基本台帳が得られれば、按分は不要になる。按分値は受領までの暫定である</t>
+          <t>要介護度別の給付費単価を用いて再計算する。第2段階（サービス見込量）の算定チェーンで確認できる</t>
         </is>
       </c>
     </row>
     <row r="20" ht="86" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>町別の判定は、社人研側の町別75歳以上が当方の按分値であることに依存している。「東神楽町の75歳以上を下方に補正する」という結論は、按分の仮定が外れれば覆る。</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>住民基本台帳側は原表の受領により按分が不要になったが、社人研側は依然として按分値である。令和2年の75歳以上/65歳以上比は東川町54.0％・美瑛町56.9％・東神楽町52.7％と差があり、この比が将来も同じ倍率で動くと仮定している。東神楽町の75歳以上の社人研値1,839人（令和7年）はこの仮定の産物である。</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>社人研「日本の地域別将来推計人口」の男女5歳階級別の市区町村別表（東川町01458・美瑛町01459・東神楽町01453）を直接取得すれば、按分は不要になる。取得までは町別の75歳以上の判定は暫定とする</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="86" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>比較期間の選び方が結果を左右する。案Aと案Bで75歳以上の補正の大きさが2倍近く異なる。</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>案A（平成24年→令和5年の11年）では年0.39ポイント、案B（令和2年→令和7年の5年）では年0.25ポイントである。平成29年から令和5年の6年で見ると年0.56ポイントとなり、判定が④に変わる。</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>複数の期間で算定し、判定が変わらないことを確かめる。変わる場合は、推計期間そのものを含む案Bを優先する理由（判定ルール⑦）を示す</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="86" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>案Bの終点は令和7年1月1日の1年のみである。この1年に一時的な変動があれば、5年の伸び率がその分だけ歪む。</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>3町計の75歳以上は令和6年5,233人から令和7年5,415人へ182人（3.5％）増えており、前年の131人（2.6％）、前々年の60人（1.2％）と比べて大きい。団塊の世代が令和6年から令和7年にかけて75歳に到達したことによるとみられるが、終点の1年に大きな増加が入っている。</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>令和8年1月1日現在の値を加えて6年で再算定する。3町計の令和8年1月1日は別途整理により65歳以上9,176人・75歳以上5,492人が得られているため、町別の内訳が出れば直ちに更新できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="86" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>軽微</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>比較期間を平成24年から令和5年としたが、この期間の選び方が結果を左右する。</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>たとえば平成29年から令和5年の6年で見ると、住基75歳以上は4,865→5,205（年+1.13％）、社人研は4,961→5,487（年+1.69％）で、年平均の差は0.56ポイントとなり判定が④に変わる。</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>複数の期間で算定し、判定が変わらないことを確かめる。変わる場合は、直近の期間を優先する理由を示す</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>注1）指摘No.1・No.2は、本表の結論（水準の補正は不要、75歳以上の伸び率のみ補正）そのものを揺るがすものである。いずれも反証条件が示されており、住所地特例の適用者数と、国勢調査・住民基本台帳の差の推移が得られれば決着する。注2）指摘No.3（適用年数のずれ）は、補正係数の算定方法に関わる。3年か4年かで補正の大きさが変わるため、計画本文に用いる前に決定する。注3）指摘No.6のとおり、比較期間の選び方で判定が変わる。町別のデータの受領後に、複数の期間で算定して安定性を確かめる。</t>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>案Bでは65歳以上が+87人増えるにもかかわらず、認定者数は-8人にとどまり、保険料は約85円下がる。「高齢者が増えるのに保険料が下がる」という結果は、説明を要する。</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>増えるのは認定率の低い前期高齢者であり、減るのは認定率の高い後期高齢者であるためである。保険料は分母（第1号被保険者数）が増えて分子（給付費）がほぼ変わらないために下がる。計算としては正しいが、協議会での説明では誤解を招きやすい。</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>04シートの注6に説明を置いた。資料では認定者数と第1号被保険者数を必ず併記する</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="78" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>注1）指摘No.1・No.2は、本表の結論（水準の補正は不要、75歳以上の伸び率のみ補正）そのものを揺るがすものである。いずれも反証条件が示されており、住所地特例の適用者数と、国勢調査・住民基本台帳の差の推移が得られれば決着する。注2）指摘No.3（適用年数のずれ）は、補正係数の算定方法に関わる。3年か4年かで補正の大きさが変わるため、計画本文に用いる前に決定する。注3）指摘No.6のとおり、比較期間の選び方で判定が変わる。案Bを採る理由は判定ルール⑦に置いた。注4）指摘No.5は、町別のデータの受領により住民基本台帳側の按分が不要になった一方で、社人研側が按分値のまま残ったため、「中」から「重大」に引き上げた。町別の75歳以上の補正方向は、社人研の市区町村別・男女5歳階級別表の取得までは暫定である。注5）指摘No.7の反証条件（令和8年1月1日の町別内訳）は、05シートの【4】④として資料提供を依頼する。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A22:E22"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx
+++ b/output/第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx
@@ -2623,7 +2623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3621,159 +3621,314 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>【4　なお必要なデータ】</t>
+          <t>【4　第9期計画の町別の調整との対照】</t>
         </is>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="4" t="inlineStr"/>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>町</t>
+        </is>
+      </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>必要なデータ</t>
+          <t>第9期計画の乖離
+（令和22年・総人口）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
-      <c r="D36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>本表の補正の向き
+（75歳以上）</t>
+        </is>
+      </c>
       <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>順序</t>
+        </is>
+      </c>
       <c r="G36" s="4" t="inlineStr"/>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>何のために必要か</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="34" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>町別の第1号被保険者数（年齢階級別・令和8年3月末）</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="16" t="n"/>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>＋18.5％</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>上方（3年で＋3.2％）</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
       <c r="G37" s="16" t="n"/>
       <c r="H37" s="16" t="n"/>
       <c r="I37" s="17" t="n"/>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>町別の補正を適用するための基準人口。65〜74歳・75〜84歳・85歳以上の3階級。現在は3町計のみである</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="34" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>町別の要介護認定者数（要介護度別・令和8年3月末）</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+          <t>第9期計画は社人研より高く（低く）見込み、本表は伸び率を上方（下方）に補正する。向きが同じである</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>＋2.9％</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>補正しない（境界）</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
       <c r="G38" s="16" t="n"/>
       <c r="H38" s="16" t="n"/>
       <c r="I38" s="17" t="n"/>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>町別の認定率を算定する。町別の見込量の算定に必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="34" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>住所地特例の適用者数（町別・令和8年3月末）</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
+          <t>第9期計画は社人研より高く（低く）見込み、本表は伸び率を上方（下方）に補正する。向きが同じである</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>▲5.2％</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>下方（3年で▲4.2％）</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
       <c r="G39" s="16" t="n"/>
       <c r="H39" s="16" t="n"/>
       <c r="I39" s="17" t="n"/>
       <c r="J39" s="5" t="inlineStr">
         <is>
+          <t>第9期計画は社人研より高く（低く）見込み、本表は伸び率を上方（下方）に補正する。向きが同じである</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="52" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>注4）第9期計画は住民基本台帳によるコーホート変化率法により町別の将来推計を行っており、社人研推計との乖離は令和22年の総人口で東川町＋18.5％・美瑛町＋2.9％・東神楽町▲5.2％であった。本表の75歳以上の補正の向きは、3町ともこれと同じ順序である。注5）ただし第9期計画の乖離は総人口、本表の補正は75歳以上の伸び率で、量が異なる。一致は傍証にとどまり、第9期計画の推計方法の妥当性を示すものではない。注6）この対照は、当方が「社人研推計をそのまま用いる」ことを案としてきたこと（別管理表 確認事項B No.5）の見直しを求めるものである。少なくとも東川町については、社人研をそのまま用いる案を再検討する必要がある［要協議］。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>【5　なお必要なデータ】</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="4" t="inlineStr"/>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>必要なデータ</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>何のために必要か</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>町別の第1号被保険者数（年齢階級別・令和8年3月末）</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="16" t="n"/>
+      <c r="G44" s="16" t="n"/>
+      <c r="H44" s="16" t="n"/>
+      <c r="I44" s="17" t="n"/>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>町別の補正を適用するための基準人口。65〜74歳・75〜84歳・85歳以上の3階級。現在は3町計のみである</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>町別の要介護認定者数（要介護度別・令和8年3月末）</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="n"/>
+      <c r="D45" s="16" t="n"/>
+      <c r="E45" s="16" t="n"/>
+      <c r="F45" s="16" t="n"/>
+      <c r="G45" s="16" t="n"/>
+      <c r="H45" s="16" t="n"/>
+      <c r="I45" s="17" t="n"/>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>町別の認定率を算定する。町別の見込量の算定に必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>住所地特例の適用者数（町別・令和8年3月末）</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="n"/>
+      <c r="D46" s="16" t="n"/>
+      <c r="E46" s="16" t="n"/>
+      <c r="F46" s="16" t="n"/>
+      <c r="G46" s="16" t="n"/>
+      <c r="H46" s="16" t="n"/>
+      <c r="I46" s="17" t="n"/>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
           <t>住民基本台帳人口と第1号被保険者数の差の説明。07シートの指摘No.1の反証条件</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="34" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>④</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>令和8年1月1日現在の年齢5歳階級別人口（町別）</t>
         </is>
       </c>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
-      <c r="G40" s="16" t="n"/>
-      <c r="H40" s="16" t="n"/>
-      <c r="I40" s="17" t="n"/>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="C47" s="16" t="n"/>
+      <c r="D47" s="16" t="n"/>
+      <c r="E47" s="16" t="n"/>
+      <c r="F47" s="16" t="n"/>
+      <c r="G47" s="16" t="n"/>
+      <c r="H47" s="16" t="n"/>
+      <c r="I47" s="17" t="n"/>
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>本シートは令和7年1月1日までである。令和8年分が公表され次第、6年の伸び率に更新する</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="39" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
+    <row r="49" ht="39" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>出所）総務省「住民基本台帳に基づく人口、人口動態及び世帯数」年齢別人口（市区町村別）【総計】各年1月1日現在。団体コードは東川町014583・美瑛町014591・東神楽町014532。社人研は「日本の地域別将来推計人口（令和5年推計）」により、介護保険事業状況報告等の見える化システムのA1・A2・A3・A4から取得した。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="39">
     <mergeCell ref="F31:I31"/>
     <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="F39:I39"/>
     <mergeCell ref="A35:J35"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="B22:I22"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="B46:I46"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A40:J40"/>
     <mergeCell ref="F29:I29"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="B23:I23"/>
+    <mergeCell ref="A49:J49"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B44:I44"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:E37"/>
     <mergeCell ref="F30:I30"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="D39:E39"/>
     <mergeCell ref="F32:I32"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="D30:E30"/>
+    <mergeCell ref="B45:I45"/>
     <mergeCell ref="A18:J18"/>
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="A27:J27"/>
     <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:I38"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A42:J42"/>

--- a/output/第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx
+++ b/output/第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_補正の適用と影響" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_町別の突合と補正方向" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_住民基本台帳の原表" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_判定ルールとレッドチーム" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_判定ルールと自己点検" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -78,17 +78,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -191,9 +191,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -203,27 +200,27 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -238,13 +235,16 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -857,9 +857,9 @@
           <t>見える化A4　社人研 令和5年推計の階級別人口</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>★伸び率にのみ効く。水準は住基のため補正不要</t>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>伸び率にのみ効く。水準は住基のため補正不要</t>
         </is>
       </c>
     </row>
@@ -1011,17 +1011,17 @@
           <t>65〜74歳</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>3,600人</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>4.03％</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>145人</t>
         </is>
@@ -1038,17 +1038,17 @@
           <t>75〜84歳</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>3,499人</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>17.52％</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>613人</t>
         </is>
@@ -1065,17 +1065,17 @@
           <t>85歳以上</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>1,990人</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>61.60％</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>1,226人</t>
         </is>
@@ -1087,27 +1087,27 @@
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>9,090人</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>1,984人</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>うち75歳以上 5,490人</t>
         </is>
@@ -1203,17 +1203,17 @@
           <t>総人口</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>27,498人</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>26,876人</t>
         </is>
@@ -1235,17 +1235,17 @@
           <t>65歳以上</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>9,090人</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>9,176人</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>9,320人</t>
         </is>
@@ -1267,29 +1267,29 @@
           <t>75歳以上</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>5,490人</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>5,492人</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>5,748人</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>-2人（-0.04％）</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>★ほぼ一致する。水準の補正は不要である</t>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>ほぼ一致する。水準の補正は不要である</t>
         </is>
       </c>
     </row>
@@ -1338,22 +1338,22 @@
           <t>総人口</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>26,876人</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>27,498人</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>+622人</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>+2.3％</t>
         </is>
@@ -1370,22 +1370,22 @@
           <t>65歳以上</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>9,320人</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>9,176人</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>-144人</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>-1.5％</t>
         </is>
@@ -1402,22 +1402,22 @@
           <t>75歳以上</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>5,748人</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>5,492人</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>-256人</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>-4.5％</t>
         </is>
@@ -1521,24 +1521,24 @@
           <t>2012年</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>4,398人</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>4,443人</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>-45人</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="16" t="n"/>
-      <c r="G6" s="17" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="15" t="n"/>
       <c r="H6" s="5" t="inlineStr">
         <is>
           <t>起点。差45人（1.0％）</t>
@@ -1551,24 +1551,24 @@
           <t>2013年</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>4,491人</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>4,570人</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>-79人</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="16" t="n"/>
-      <c r="G7" s="17" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="15" t="n"/>
       <c r="H7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1577,24 +1577,24 @@
           <t>2014年</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>4,578人</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>4,696人</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>-118人</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="16" t="n"/>
-      <c r="G8" s="17" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="15" t="n"/>
       <c r="H8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -1603,24 +1603,24 @@
           <t>2015年</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>4,667人</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>4,823人</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>-156人</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="17" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="15" t="n"/>
       <c r="H9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -1629,24 +1629,24 @@
           <t>2016年</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>4,768人</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>4,892人</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>-124人</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="17" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="15" t="n"/>
       <c r="H10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -1655,24 +1655,24 @@
           <t>2017年</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>4,865人</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>4,961人</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>-96人</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="17" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="15" t="n"/>
       <c r="H11" s="5" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -1681,24 +1681,24 @@
           <t>2018年</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>4,933人</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>5,029人</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>-96人</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="17" t="n"/>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="15" t="n"/>
       <c r="H12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1707,24 +1707,24 @@
           <t>2019年</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>5,006人</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>5,098人</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>-92人</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="17" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="15" t="n"/>
       <c r="H13" s="5" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -1733,24 +1733,24 @@
           <t>2020年</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>5,014人</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>5,167人</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>-153人</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="17" t="n"/>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="15" t="n"/>
       <c r="H14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1759,24 +1759,24 @@
           <t>2021年</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>5,039人</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>5,274人</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>-235人</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="17" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="15" t="n"/>
       <c r="H15" s="5" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1785,24 +1785,24 @@
           <t>2022年</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>5,109人</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>5,380人</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>-271人</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="17" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="15" t="n"/>
       <c r="H16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1811,24 +1811,24 @@
           <t>2023年</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>5,205人</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>5,487人</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>-282人</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="17" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="15" t="n"/>
       <c r="H17" s="5" t="inlineStr">
         <is>
           <t>終点。差282人（5.4％）。11年で差が237人拡大した</t>
@@ -1890,39 +1890,39 @@
           <t>75歳以上</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>+18.35％</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>+23.50％</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>-5.15pt</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>+1.54％</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>+1.94％</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>-0.394pt</t>
         </is>
       </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>★社人研が速い。下方補正の対象</t>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>社人研が速い。下方補正の対象</t>
         </is>
       </c>
     </row>
@@ -1932,37 +1932,37 @@
           <t>65歳以上</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>+12.88％</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>+12.14％</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>+0.75pt</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>+1.11％</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>+1.05％</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>+0.061pt</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>ほぼ一致。補正を要しない</t>
         </is>
@@ -2012,11 +2012,11 @@
           <t>社人研の伸び率を、住民基本台帳の伸び率との比（(1＋年0.0154)÷(1＋年0.0194)）で割り引く。基準年度（令和8年度）から令和11年度までの3年に適用する。</t>
         </is>
       </c>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="17" t="n"/>
-      <c r="G26" s="19" t="inlineStr">
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="18" t="inlineStr">
         <is>
           <t>0.9885</t>
         </is>
@@ -2038,11 +2038,11 @@
           <t>住民基本台帳の伸び率が社人研をわずかに上回るが、差は年0.06ポイントで補正の閾値（年0.2ポイント）に達しない。補正しない。</t>
         </is>
       </c>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="17" t="n"/>
-      <c r="G27" s="12" t="inlineStr">
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>1.0018</t>
         </is>
@@ -2056,7 +2056,7 @@
     <row r="29" ht="52" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>注1）比較期間を平成24年から令和5年としたのは、住民基本台帳と社人研（見える化）が同じ時点で揃う唯一の期間だからである。令和5年より後の住民基本台帳は、町別の年齢5歳階級別の受領後に延長する。注2）社人研の令和5年までの値は推計値ではなく国勢調査による実績の補間である。つまり両者の差は「推計の精度」ではなく「国勢調査と住民基本台帳の統計の差」を含む。この点は06シート（レッドチーム）の指摘No.2で扱う。注3）65歳以上の補正の閾値を年0.2ポイントとしたのは受託者の設定であり、決定ではない（06シート）。</t>
+          <t>注1）比較期間を平成24年から令和5年としたのは、住民基本台帳と社人研（見える化）が同じ時点で揃う唯一の期間だからである。令和5年より後の住民基本台帳は、町別の年齢5歳階級別の受領後に延長する。注2）社人研の令和5年までの値は推計値ではなく国勢調査による実績の補間である。つまり両者の差は「推計の精度」ではなく「国勢調査と住民基本台帳の統計の差」を含む。この点は06シート（自己点検）の指摘No.2で扱う。注3）65歳以上の補正の閾値を年0.2ポイントとしたのは受託者の設定であり、決定ではない（06シート）。</t>
         </is>
       </c>
     </row>
@@ -2162,22 +2162,22 @@
           <t>65〜74歳</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>3,403人</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>3,403人</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>+0人</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>+0.00％</t>
         </is>
@@ -2194,22 +2194,22 @@
           <t>75〜84歳</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>3,597人</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>3,556人</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>-42人</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>-1.15％</t>
         </is>
@@ -2226,22 +2226,22 @@
           <t>85歳以上</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>2,072人</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>2,048人</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>-24人</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>-1.15％</t>
         </is>
@@ -2253,64 +2253,64 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>65歳以上　計</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>9,072人</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>9,006人</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>-65人</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>-0.72％</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>保険料の分母（第1号被保険者数）になる</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>認定者数</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>2,004人</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>1,983人</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>-22人</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>-1.08％</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>給付費に比例する。認定率はトレンド継続の置き方による</t>
         </is>
@@ -2361,22 +2361,22 @@
           <t>給付費（指数）</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>1.0000</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>0.9892</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>-0.0108</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>-1.08％</t>
         </is>
@@ -2393,22 +2393,22 @@
           <t>第1号被保険者数（指数）</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>1.0000</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>0.9928</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>-0.0072</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>-0.72％</t>
         </is>
@@ -2420,32 +2420,32 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>保険料基準額</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>6,238円</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>約6,216円</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>-22円</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>-0.36％</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>自然体推計の第10期3年平均6,238円に、上記の比を適用した概算</t>
         </is>
@@ -2510,17 +2510,17 @@
           <t>社人研の伸び率をそのまま用いる</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>9,072人</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>2,004人</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>6,238円</t>
         </is>
@@ -2543,17 +2543,17 @@
           <t>平成24年→令和5年の11年で算定。75歳以上のみ1.15％下方に補正</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>9,006人</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>1,983人</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>約6,216円（-22円）</t>
         </is>
@@ -2565,35 +2565,35 @@
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>案B
 推計期間ベース</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>令和2年→令和7年の5年で算定。65〜74歳を+3.77％、75歳以上を0.73％補正</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>9,159人</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>1,996人</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E24" s="19" t="inlineStr">
         <is>
           <t>約6,153円（-85円）</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>★こちらを採る。社人研 令和5年推計の基準年から第1推計年までの区間であり、推計そのものを実績で検証している</t>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>こちらを採る。社人研 令和5年推計の基準年から第1推計年までの区間であり、推計そのものを実績で検証している</t>
         </is>
       </c>
     </row>
@@ -2729,42 +2729,42 @@
           <t>65〜74歳</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>1,279人</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>1,085人</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>-3.24％</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>1,270人</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>1,070人</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>-3.37％</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>-0.13pt</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>補正しない（3年で+0.4％）</t>
         </is>
@@ -2777,90 +2777,90 @@
           <t>75歳以上</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>1,418人</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>1,637人</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>+2.91％</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>1,490人</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>1,632人</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>+1.83％</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>-1.08pt</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>上方に補正（3年で+3.2％）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="22" t="inlineStr"/>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr"/>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>65歳以上</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>2,697人</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>2,722人</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>+0.18％</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>2,760人</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>2,702人</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>-0.43％</t>
         </is>
       </c>
-      <c r="I8" s="23" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>-0.61pt</t>
         </is>
       </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>上方に補正（3年で+1.8％）</t>
         </is>
@@ -2877,42 +2877,42 @@
           <t>65〜74歳</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>1,609人</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>1,402人</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>-2.72％</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>1,617人</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>1,274人</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>-4.66％</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>-1.94pt</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>上方に補正（3年で+6.2％）</t>
         </is>
@@ -2925,90 +2925,90 @@
           <t>75歳以上</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>2,151人</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>2,226人</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>+0.69％</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>2,134人</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>2,230人</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>+0.88％</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>+0.20pt</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>補正しない（3年で-0.6％）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="22" t="inlineStr"/>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr"/>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>65歳以上</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>3,760人</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>3,628人</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>-0.71％</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>3,751人</t>
         </is>
       </c>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>3,504人</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>-1.35％</t>
         </is>
       </c>
-      <c r="I11" s="23" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>-0.64pt</t>
         </is>
       </c>
-      <c r="J11" s="22" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t>上方に補正（3年で+2.0％）</t>
         </is>
@@ -3025,42 +3025,42 @@
           <t>65〜74歳</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>1,343人</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>1,330人</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>-0.19％</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>1,384人</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>1,280人</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>-1.55％</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>-1.36pt</t>
         </is>
       </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>上方に補正（3年で+4.2％）</t>
         </is>
@@ -3073,90 +3073,90 @@
           <t>75歳以上</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>1,399人</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>1,552人</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>+2.10％</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>1,543人</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>1,839人</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>+3.58％</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>+1.48pt</t>
         </is>
       </c>
-      <c r="J13" s="18" t="inlineStr">
+      <c r="J13" s="16" t="inlineStr">
         <is>
           <t>下方に補正（3年で-4.2％）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="22" t="inlineStr"/>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr"/>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>65歳以上</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>2,742人</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>2,882人</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>+1.00％</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>2,927人</t>
         </is>
       </c>
-      <c r="G14" s="23" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>3,119人</t>
         </is>
       </c>
-      <c r="H14" s="23" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>+1.28％</t>
         </is>
       </c>
-      <c r="I14" s="23" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>+0.28pt</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t>下方に補正（3年で-0.8％）</t>
         </is>
@@ -3173,42 +3173,42 @@
           <t>65〜74歳</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>4,231人</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>3,817人</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>-2.04％</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>4,270人</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>3,622人</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>-3.24％</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>-1.20pt</t>
         </is>
       </c>
-      <c r="J15" s="21" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>上方に補正（3年で+3.8％）</t>
         </is>
@@ -3221,90 +3221,90 @@
           <t>75歳以上</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>4,968人</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>5,415人</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>+1.74％</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>5,167人</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>5,701人</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>+1.99％</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>+0.25pt</t>
         </is>
       </c>
-      <c r="J16" s="18" t="inlineStr">
+      <c r="J16" s="16" t="inlineStr">
         <is>
           <t>下方に補正（3年で-0.7％）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="22" t="inlineStr"/>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr"/>
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>65歳以上</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>9,199人</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>9,232人</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>+0.07％</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>9,437人</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>9,323人</t>
         </is>
       </c>
-      <c r="H17" s="23" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>-0.24％</t>
         </is>
       </c>
-      <c r="I17" s="23" t="inlineStr">
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>-0.31pt</t>
         </is>
       </c>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t>上方に補正（3年で+0.9％）</t>
         </is>
@@ -3359,13 +3359,13 @@
           <t>65〜74歳は社人研とほぼ一致する（差-0.13ポイント）。75歳以上は住民基本台帳の方が速く（差-1.08ポイント）、3年で+3.2％の上方補正となる。3町で唯一、75歳以上を上方に補正する町である。</t>
         </is>
       </c>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n"/>
-      <c r="H22" s="16" t="n"/>
-      <c r="I22" s="17" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="15" t="n"/>
       <c r="J22" s="5" t="inlineStr">
         <is>
           <t>総人口が令和2年から令和7年にかけて8,380人から8,673人へ293人増えた3町で唯一の町である。社人研は同期間に減少を見込んでいた。移住施策による転入が75歳以上の増加を上回る速度で総人口を押し上げている一方、75歳以上そのものも実績の方が速く増えている</t>
@@ -3383,13 +3383,13 @@
           <t>65〜74歳は社人研の減少見込みが実績より大幅に速く（差-1.94ポイント）、3年で+6.2％の上方補正となる。75歳以上は差が+0.20ポイントで補正しない。</t>
         </is>
       </c>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16" t="n"/>
-      <c r="E23" s="16" t="n"/>
-      <c r="F23" s="16" t="n"/>
-      <c r="G23" s="16" t="n"/>
-      <c r="H23" s="16" t="n"/>
-      <c r="I23" s="17" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="15" t="n"/>
       <c r="J23" s="5" t="inlineStr">
         <is>
           <t>3町で最も高齢化率が高く（令和7年39.1％）、総人口の減少も最も速い。社人研は令和2年から令和7年に775人の減少を見込んでいたが、実績は629人の減少にとどまった。前期高齢者が想定ほど減っていないことが乖離の主因である</t>
@@ -3407,13 +3407,13 @@
           <t>65〜74歳は3年で+4.2％の上方補正、75歳以上は社人研が年+1.48ポイント速く、3年で4.2％の下方補正となる。3町で唯一、75歳以上を下方に補正する町である。</t>
         </is>
       </c>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
-      <c r="G24" s="16" t="n"/>
-      <c r="H24" s="16" t="n"/>
-      <c r="I24" s="17" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="15" t="n"/>
       <c r="J24" s="5" t="inlineStr">
         <is>
           <t>3町計で75歳以上に下方補正が生じる原因は、実質的にこの町にある。社人研は令和7年の75歳以上を1,839人と見込んでいたが、実績は1,552人で287人少ない。旭川市に隣接し人口構成が若い町で、後期高齢化の速度が推計より緩やかである</t>
@@ -3421,24 +3421,24 @@
       </c>
     </row>
     <row r="25" ht="76" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>3町計</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>65〜74歳は3年で+3.8％の上方補正、75歳以上は3年で0.7％の下方補正となる。両者を合わせた65歳以上は3年で+0.9％の上方となる。</t>
         </is>
       </c>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
-      <c r="G25" s="16" t="n"/>
-      <c r="H25" s="16" t="n"/>
-      <c r="I25" s="17" t="n"/>
-      <c r="J25" s="10" t="inlineStr">
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="14" t="n"/>
+      <c r="H25" s="14" t="n"/>
+      <c r="I25" s="15" t="n"/>
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>3町計では、前期高齢者の上方補正が後期高齢者の下方補正を上回る。認定率が高いのは後期高齢者であるため、認定者数への影響は65歳以上の増加ほどには大きくならない</t>
         </is>
@@ -3489,26 +3489,26 @@
           <t>東川町</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>1.0000</t>
         </is>
       </c>
-      <c r="C29" s="17" t="n"/>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>1.0322</t>
         </is>
       </c>
-      <c r="E29" s="17" t="n"/>
+      <c r="E29" s="15" t="n"/>
       <c r="F29" s="5" t="inlineStr">
         <is>
           <t>適用は保留　←　町別の基準人口が未受領</t>
         </is>
       </c>
-      <c r="G29" s="16" t="n"/>
-      <c r="H29" s="16" t="n"/>
-      <c r="I29" s="17" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="15" t="n"/>
       <c r="J29" s="5" t="inlineStr">
         <is>
           <t>社人研側の町別75歳以上は当方の按分値である。町別の公表値ではない</t>
@@ -3521,26 +3521,26 @@
           <t>美瑛町</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>1.0624</t>
         </is>
       </c>
-      <c r="C30" s="17" t="n"/>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>1.0000</t>
         </is>
       </c>
-      <c r="E30" s="17" t="n"/>
+      <c r="E30" s="15" t="n"/>
       <c r="F30" s="5" t="inlineStr">
         <is>
           <t>適用は保留　←　町別の基準人口が未受領</t>
         </is>
       </c>
-      <c r="G30" s="16" t="n"/>
-      <c r="H30" s="16" t="n"/>
-      <c r="I30" s="17" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="15" t="n"/>
       <c r="J30" s="5" t="inlineStr">
         <is>
           <t>社人研側の町別75歳以上は当方の按分値である。町別の公表値ではない</t>
@@ -3553,26 +3553,26 @@
           <t>東神楽町</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>1.0420</t>
         </is>
       </c>
-      <c r="C31" s="17" t="n"/>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>0.9578</t>
         </is>
       </c>
-      <c r="E31" s="17" t="n"/>
+      <c r="E31" s="15" t="n"/>
       <c r="F31" s="5" t="inlineStr">
         <is>
           <t>適用は保留　←　町別の基準人口が未受領</t>
         </is>
       </c>
-      <c r="G31" s="16" t="n"/>
-      <c r="H31" s="16" t="n"/>
-      <c r="I31" s="17" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="15" t="n"/>
       <c r="J31" s="5" t="inlineStr">
         <is>
           <t>社人研側の町別75歳以上は当方の按分値である。町別の公表値ではない</t>
@@ -3580,32 +3580,32 @@
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>3町計</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>1.0377</t>
         </is>
       </c>
-      <c r="C32" s="17" t="n"/>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>0.9927</t>
         </is>
       </c>
-      <c r="E32" s="17" t="n"/>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="9" t="inlineStr">
         <is>
           <t>適用できる</t>
         </is>
       </c>
-      <c r="G32" s="16" t="n"/>
-      <c r="H32" s="16" t="n"/>
-      <c r="I32" s="17" t="n"/>
-      <c r="J32" s="10" t="inlineStr">
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="14" t="n"/>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -3665,26 +3665,26 @@
           <t>東川町</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>＋18.5％</t>
         </is>
       </c>
-      <c r="C37" s="17" t="n"/>
+      <c r="C37" s="15" t="n"/>
       <c r="D37" s="5" t="inlineStr">
         <is>
           <t>上方（3年で＋3.2％）</t>
         </is>
       </c>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
       </c>
-      <c r="G37" s="16" t="n"/>
-      <c r="H37" s="16" t="n"/>
-      <c r="I37" s="17" t="n"/>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="15" t="n"/>
       <c r="J37" s="5" t="inlineStr">
         <is>
           <t>第9期計画は社人研より高く（低く）見込み、本表は伸び率を上方（下方）に補正する。向きが同じである</t>
@@ -3697,26 +3697,26 @@
           <t>美瑛町</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>＋2.9％</t>
         </is>
       </c>
-      <c r="C38" s="17" t="n"/>
+      <c r="C38" s="15" t="n"/>
       <c r="D38" s="5" t="inlineStr">
         <is>
           <t>補正しない（境界）</t>
         </is>
       </c>
-      <c r="E38" s="17" t="n"/>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
       </c>
-      <c r="G38" s="16" t="n"/>
-      <c r="H38" s="16" t="n"/>
-      <c r="I38" s="17" t="n"/>
+      <c r="G38" s="14" t="n"/>
+      <c r="H38" s="14" t="n"/>
+      <c r="I38" s="15" t="n"/>
       <c r="J38" s="5" t="inlineStr">
         <is>
           <t>第9期計画は社人研より高く（低く）見込み、本表は伸び率を上方（下方）に補正する。向きが同じである</t>
@@ -3729,26 +3729,26 @@
           <t>東神楽町</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>▲5.2％</t>
         </is>
       </c>
-      <c r="C39" s="17" t="n"/>
+      <c r="C39" s="15" t="n"/>
       <c r="D39" s="5" t="inlineStr">
         <is>
           <t>下方（3年で▲4.2％）</t>
         </is>
       </c>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
       </c>
-      <c r="G39" s="16" t="n"/>
-      <c r="H39" s="16" t="n"/>
-      <c r="I39" s="17" t="n"/>
+      <c r="G39" s="14" t="n"/>
+      <c r="H39" s="14" t="n"/>
+      <c r="I39" s="15" t="n"/>
       <c r="J39" s="5" t="inlineStr">
         <is>
           <t>第9期計画は社人研より高く（低く）見込み、本表は伸び率を上方（下方）に補正する。向きが同じである</t>
@@ -3795,18 +3795,18 @@
           <t>①</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="24" t="inlineStr">
         <is>
           <t>町別の第1号被保険者数（年齢階級別・令和8年3月末）</t>
         </is>
       </c>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
-      <c r="G44" s="16" t="n"/>
-      <c r="H44" s="16" t="n"/>
-      <c r="I44" s="17" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="14" t="n"/>
+      <c r="E44" s="14" t="n"/>
+      <c r="F44" s="14" t="n"/>
+      <c r="G44" s="14" t="n"/>
+      <c r="H44" s="14" t="n"/>
+      <c r="I44" s="15" t="n"/>
       <c r="J44" s="5" t="inlineStr">
         <is>
           <t>町別の補正を適用するための基準人口。65〜74歳・75〜84歳・85歳以上の3階級。現在は3町計のみである</t>
@@ -3819,18 +3819,18 @@
           <t>②</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="24" t="inlineStr">
         <is>
           <t>町別の要介護認定者数（要介護度別・令和8年3月末）</t>
         </is>
       </c>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
-      <c r="G45" s="16" t="n"/>
-      <c r="H45" s="16" t="n"/>
-      <c r="I45" s="17" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="14" t="n"/>
+      <c r="F45" s="14" t="n"/>
+      <c r="G45" s="14" t="n"/>
+      <c r="H45" s="14" t="n"/>
+      <c r="I45" s="15" t="n"/>
       <c r="J45" s="5" t="inlineStr">
         <is>
           <t>町別の認定率を算定する。町別の見込量の算定に必要</t>
@@ -3843,18 +3843,18 @@
           <t>③</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="24" t="inlineStr">
         <is>
           <t>住所地特例の適用者数（町別・令和8年3月末）</t>
         </is>
       </c>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
-      <c r="G46" s="16" t="n"/>
-      <c r="H46" s="16" t="n"/>
-      <c r="I46" s="17" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="14" t="n"/>
+      <c r="E46" s="14" t="n"/>
+      <c r="F46" s="14" t="n"/>
+      <c r="G46" s="14" t="n"/>
+      <c r="H46" s="14" t="n"/>
+      <c r="I46" s="15" t="n"/>
       <c r="J46" s="5" t="inlineStr">
         <is>
           <t>住民基本台帳人口と第1号被保険者数の差の説明。07シートの指摘No.1の反証条件</t>
@@ -3867,18 +3867,18 @@
           <t>④</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="24" t="inlineStr">
         <is>
           <t>令和8年1月1日現在の年齢5歳階級別人口（町別）</t>
         </is>
       </c>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
-      <c r="G47" s="16" t="n"/>
-      <c r="H47" s="16" t="n"/>
-      <c r="I47" s="17" t="n"/>
+      <c r="C47" s="14" t="n"/>
+      <c r="D47" s="14" t="n"/>
+      <c r="E47" s="14" t="n"/>
+      <c r="F47" s="14" t="n"/>
+      <c r="G47" s="14" t="n"/>
+      <c r="H47" s="14" t="n"/>
+      <c r="I47" s="15" t="n"/>
       <c r="J47" s="5" t="inlineStr">
         <is>
           <t>本シートは令和7年1月1日までである。令和8年分が公表され次第、6年の伸び率に更新する</t>
@@ -4056,62 +4056,62 @@
           <t>平成31年</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>8,382</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>594</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>402</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>287</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>2,699</t>
         </is>
       </c>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t>1,410</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>32.2％</t>
         </is>
@@ -4123,62 +4123,62 @@
           <t>令和2年</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>8,380</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>647</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>503</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>399</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>296</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>165</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>2,697</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr">
         <is>
           <t>1,418</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>32.2％</t>
         </is>
@@ -4190,62 +4190,62 @@
           <t>令和3年</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>8,437</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>571</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>702</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>502</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>408</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>302</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>2,718</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="L8" s="8" t="inlineStr">
         <is>
           <t>1,445</t>
         </is>
       </c>
-      <c r="M8" s="9" t="inlineStr">
+      <c r="M8" s="8" t="inlineStr">
         <is>
           <t>32.2％</t>
         </is>
@@ -4257,62 +4257,62 @@
           <t>令和4年</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>8,390</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>528</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>714</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>514</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>410</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>318</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>2,718</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="L9" s="8" t="inlineStr">
         <is>
           <t>1,476</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="8" t="inlineStr">
         <is>
           <t>32.4％</t>
         </is>
@@ -4324,62 +4324,62 @@
           <t>令和5年</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>8,601</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>486</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>715</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>522</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>428</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>310</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>187</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>2,715</t>
         </is>
       </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="L10" s="8" t="inlineStr">
         <is>
           <t>1,514</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="8" t="inlineStr">
         <is>
           <t>31.6％</t>
         </is>
@@ -4391,62 +4391,62 @@
           <t>令和6年</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>8,576</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>472</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>676</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>441</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>297</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>2,692</t>
         </is>
       </c>
-      <c r="L11" s="9" t="inlineStr">
+      <c r="L11" s="8" t="inlineStr">
         <is>
           <t>1,544</t>
         </is>
       </c>
-      <c r="M11" s="9" t="inlineStr">
+      <c r="M11" s="8" t="inlineStr">
         <is>
           <t>31.4％</t>
         </is>
@@ -4458,69 +4458,69 @@
           <t>令和7年</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>8,673</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>453</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>632</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>614</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>453</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>322</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>171</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="J12" s="9" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>2,722</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr">
+      <c r="L12" s="8" t="inlineStr">
         <is>
           <t>1,637</t>
         </is>
       </c>
-      <c r="M12" s="9" t="inlineStr">
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>31.4％</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>5年の増減
 （令和2→7年）</t>
@@ -4667,62 +4667,62 @@
           <t>平成31年</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>10,043</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>859</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>759</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>726</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>652</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>455</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>236</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>3,764</t>
         </is>
       </c>
-      <c r="L17" s="9" t="inlineStr">
+      <c r="L17" s="8" t="inlineStr">
         <is>
           <t>2,146</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>37.5％</t>
         </is>
@@ -4734,62 +4734,62 @@
           <t>令和2年</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>9,912</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>809</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>729</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>637</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>479</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>235</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>3,760</t>
         </is>
       </c>
-      <c r="L18" s="9" t="inlineStr">
+      <c r="L18" s="8" t="inlineStr">
         <is>
           <t>2,151</t>
         </is>
       </c>
-      <c r="M18" s="9" t="inlineStr">
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t>37.9％</t>
         </is>
@@ -4801,62 +4801,62 @@
           <t>令和3年</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>9,775</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>788</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>833</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>662</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>645</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>248</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>3,757</t>
         </is>
       </c>
-      <c r="L19" s="9" t="inlineStr">
+      <c r="L19" s="8" t="inlineStr">
         <is>
           <t>2,136</t>
         </is>
       </c>
-      <c r="M19" s="9" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>38.4％</t>
         </is>
@@ -4868,62 +4868,62 @@
           <t>令和4年</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>9,636</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>718</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>869</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>637</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>652</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>503</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>251</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>3,720</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr">
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t>2,133</t>
         </is>
       </c>
-      <c r="M20" s="9" t="inlineStr">
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t>38.6％</t>
         </is>
@@ -4935,62 +4935,62 @@
           <t>令和5年</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>9,573</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>698</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>840</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>657</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>651</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>475</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>275</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>3,696</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr">
+      <c r="L21" s="8" t="inlineStr">
         <is>
           <t>2,158</t>
         </is>
       </c>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="M21" s="8" t="inlineStr">
         <is>
           <t>38.6％</t>
         </is>
@@ -5002,62 +5002,62 @@
           <t>令和6年</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>9,432</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>636</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>820</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>701</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>633</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>493</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>275</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>3,653</t>
         </is>
       </c>
-      <c r="L22" s="9" t="inlineStr">
+      <c r="L22" s="8" t="inlineStr">
         <is>
           <t>2,197</t>
         </is>
       </c>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="M22" s="8" t="inlineStr">
         <is>
           <t>38.7％</t>
         </is>
@@ -5069,69 +5069,69 @@
           <t>令和7年</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>9,283</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>770</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>728</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>631</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>487</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>295</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>3,628</t>
         </is>
       </c>
-      <c r="L23" s="9" t="inlineStr">
+      <c r="L23" s="8" t="inlineStr">
         <is>
           <t>2,226</t>
         </is>
       </c>
-      <c r="M23" s="9" t="inlineStr">
+      <c r="M23" s="8" t="inlineStr">
         <is>
           <t>39.1％</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>5年の増減
 （令和2→7年）</t>
@@ -5278,62 +5278,62 @@
           <t>平成31年</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>10,321</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>715</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>589</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>491</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>422</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>287</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>135</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr">
+      <c r="J28" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="K28" s="8" t="inlineStr">
         <is>
           <t>2,683</t>
         </is>
       </c>
-      <c r="L28" s="9" t="inlineStr">
+      <c r="L28" s="8" t="inlineStr">
         <is>
           <t>1,379</t>
         </is>
       </c>
-      <c r="M28" s="9" t="inlineStr">
+      <c r="M28" s="8" t="inlineStr">
         <is>
           <t>26.0％</t>
         </is>
@@ -5345,62 +5345,62 @@
           <t>令和2年</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>10,239</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>693</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>650</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>503</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>409</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>307</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>139</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr">
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K29" s="9" t="inlineStr">
+      <c r="K29" s="8" t="inlineStr">
         <is>
           <t>2,742</t>
         </is>
       </c>
-      <c r="L29" s="9" t="inlineStr">
+      <c r="L29" s="8" t="inlineStr">
         <is>
           <t>1,399</t>
         </is>
       </c>
-      <c r="M29" s="9" t="inlineStr">
+      <c r="M29" s="8" t="inlineStr">
         <is>
           <t>26.8％</t>
         </is>
@@ -5412,62 +5412,62 @@
           <t>令和3年</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>10,154</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>686</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>693</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>396</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>308</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>143</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="J30" s="8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K30" s="8" t="inlineStr">
         <is>
           <t>2,776</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr">
+      <c r="L30" s="8" t="inlineStr">
         <is>
           <t>1,397</t>
         </is>
       </c>
-      <c r="M30" s="9" t="inlineStr">
+      <c r="M30" s="8" t="inlineStr">
         <is>
           <t>27.3％</t>
         </is>
@@ -5479,62 +5479,62 @@
           <t>令和4年</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>10,110</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>703</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>504</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>409</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>306</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="J31" s="9" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="K31" s="8" t="inlineStr">
         <is>
           <t>2,823</t>
         </is>
       </c>
-      <c r="L31" s="9" t="inlineStr">
+      <c r="L31" s="8" t="inlineStr">
         <is>
           <t>1,433</t>
         </is>
       </c>
-      <c r="M31" s="9" t="inlineStr">
+      <c r="M31" s="8" t="inlineStr">
         <is>
           <t>27.9％</t>
         </is>
@@ -5546,62 +5546,62 @@
           <t>令和5年</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>9,945</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>675</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>729</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>508</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>411</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>301</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="J32" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K32" s="8" t="inlineStr">
         <is>
           <t>2,834</t>
         </is>
       </c>
-      <c r="L32" s="9" t="inlineStr">
+      <c r="L32" s="8" t="inlineStr">
         <is>
           <t>1,430</t>
         </is>
       </c>
-      <c r="M32" s="9" t="inlineStr">
+      <c r="M32" s="8" t="inlineStr">
         <is>
           <t>28.5％</t>
         </is>
@@ -5613,62 +5613,62 @@
           <t>令和6年</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>9,862</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>653</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>701</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>541</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>430</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>318</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K33" s="8" t="inlineStr">
         <is>
           <t>2,846</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t>1,492</t>
         </is>
       </c>
-      <c r="M33" s="9" t="inlineStr">
+      <c r="M33" s="8" t="inlineStr">
         <is>
           <t>28.9％</t>
         </is>
@@ -5680,69 +5680,69 @@
           <t>令和7年</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>9,775</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>667</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>663</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>436</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>305</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>165</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K34" s="8" t="inlineStr">
         <is>
           <t>2,882</t>
         </is>
       </c>
-      <c r="L34" s="9" t="inlineStr">
+      <c r="L34" s="8" t="inlineStr">
         <is>
           <t>1,552</t>
         </is>
       </c>
-      <c r="M34" s="9" t="inlineStr">
+      <c r="M34" s="8" t="inlineStr">
         <is>
           <t>29.5％</t>
         </is>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>5年の増減
 （令和2→7年）</t>
@@ -5884,476 +5884,476 @@
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>平成31年</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>28,746</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>2,269</t>
         </is>
       </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>1,942</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>1,716</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>1,476</t>
         </is>
       </c>
-      <c r="G39" s="11" t="inlineStr">
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>1,029</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>537</t>
         </is>
       </c>
-      <c r="I39" s="11" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr">
+      <c r="J39" s="10" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="K39" s="11" t="inlineStr">
+      <c r="K39" s="10" t="inlineStr">
         <is>
           <t>9,146</t>
         </is>
       </c>
-      <c r="L39" s="11" t="inlineStr">
+      <c r="L39" s="10" t="inlineStr">
         <is>
           <t>4,935</t>
         </is>
       </c>
-      <c r="M39" s="11" t="inlineStr">
+      <c r="M39" s="10" t="inlineStr">
         <is>
           <t>31.8％</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>令和2年</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>28,531</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>2,134</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>2,097</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>1,735</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>1,445</t>
         </is>
       </c>
-      <c r="G40" s="11" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>1,082</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>539</t>
         </is>
       </c>
-      <c r="I40" s="11" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr">
+      <c r="J40" s="10" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="K40" s="11" t="inlineStr">
+      <c r="K40" s="10" t="inlineStr">
         <is>
           <t>9,199</t>
         </is>
       </c>
-      <c r="L40" s="11" t="inlineStr">
+      <c r="L40" s="10" t="inlineStr">
         <is>
           <t>4,968</t>
         </is>
       </c>
-      <c r="M40" s="11" t="inlineStr">
+      <c r="M40" s="10" t="inlineStr">
         <is>
           <t>32.2％</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="24" t="inlineStr">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>令和3年</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>28,366</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>2,045</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="D41" s="10" t="inlineStr">
         <is>
           <t>2,228</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>1,663</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>1,449</t>
         </is>
       </c>
-      <c r="G41" s="11" t="inlineStr">
+      <c r="G41" s="10" t="inlineStr">
         <is>
           <t>1,107</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>571</t>
         </is>
       </c>
-      <c r="I41" s="11" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr">
+      <c r="J41" s="10" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="K41" s="11" t="inlineStr">
+      <c r="K41" s="10" t="inlineStr">
         <is>
           <t>9,251</t>
         </is>
       </c>
-      <c r="L41" s="11" t="inlineStr">
+      <c r="L41" s="10" t="inlineStr">
         <is>
           <t>4,978</t>
         </is>
       </c>
-      <c r="M41" s="11" t="inlineStr">
+      <c r="M41" s="10" t="inlineStr">
         <is>
           <t>32.6％</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t>令和4年</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>28,136</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>1,933</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>2,286</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>1,655</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>1,471</t>
         </is>
       </c>
-      <c r="G42" s="11" t="inlineStr">
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>1,127</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>580</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr">
+      <c r="J42" s="10" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K42" s="11" t="inlineStr">
+      <c r="K42" s="10" t="inlineStr">
         <is>
           <t>9,261</t>
         </is>
       </c>
-      <c r="L42" s="11" t="inlineStr">
+      <c r="L42" s="10" t="inlineStr">
         <is>
           <t>5,042</t>
         </is>
       </c>
-      <c r="M42" s="11" t="inlineStr">
+      <c r="M42" s="10" t="inlineStr">
         <is>
           <t>32.9％</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="24" t="inlineStr">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t>令和5年</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>28,119</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>1,859</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>2,284</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>1,687</t>
         </is>
       </c>
-      <c r="F43" s="11" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>1,490</t>
         </is>
       </c>
-      <c r="G43" s="11" t="inlineStr">
+      <c r="G43" s="10" t="inlineStr">
         <is>
           <t>1,086</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>619</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>193</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr">
+      <c r="J43" s="10" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="K43" s="11" t="inlineStr">
+      <c r="K43" s="10" t="inlineStr">
         <is>
           <t>9,245</t>
         </is>
       </c>
-      <c r="L43" s="11" t="inlineStr">
+      <c r="L43" s="10" t="inlineStr">
         <is>
           <t>5,102</t>
         </is>
       </c>
-      <c r="M43" s="11" t="inlineStr">
+      <c r="M43" s="10" t="inlineStr">
         <is>
           <t>32.9％</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="24" t="inlineStr">
+      <c r="A44" s="23" t="inlineStr">
         <is>
           <t>令和6年</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>27,870</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>1,761</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>2,197</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>1,796</t>
         </is>
       </c>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>1,504</t>
         </is>
       </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>1,108</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>603</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr">
+      <c r="J44" s="10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K44" s="11" t="inlineStr">
+      <c r="K44" s="10" t="inlineStr">
         <is>
           <t>9,191</t>
         </is>
       </c>
-      <c r="L44" s="11" t="inlineStr">
+      <c r="L44" s="10" t="inlineStr">
         <is>
           <t>5,233</t>
         </is>
       </c>
-      <c r="M44" s="11" t="inlineStr">
+      <c r="M44" s="10" t="inlineStr">
         <is>
           <t>33.0％</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="24" t="inlineStr">
+      <c r="A45" s="23" t="inlineStr">
         <is>
           <t>令和7年</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>27,731</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>1,752</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>2,065</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>1,935</t>
         </is>
       </c>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>1,520</t>
         </is>
       </c>
-      <c r="G45" s="11" t="inlineStr">
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>1,114</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>631</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr">
+      <c r="J45" s="10" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="K45" s="11" t="inlineStr">
+      <c r="K45" s="10" t="inlineStr">
         <is>
           <t>9,232</t>
         </is>
       </c>
-      <c r="L45" s="11" t="inlineStr">
+      <c r="L45" s="10" t="inlineStr">
         <is>
           <t>5,415</t>
         </is>
       </c>
-      <c r="M45" s="11" t="inlineStr">
+      <c r="M45" s="10" t="inlineStr">
         <is>
           <t>33.3％</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>5年の増減
 （令和2→7年）</t>
@@ -6516,7 +6516,7 @@
           <t>推計の基準人口が住民基本台帳による場合</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>補正しない</t>
         </is>
@@ -6543,7 +6543,7 @@
           <t>年平均の差が0.2ポイント未満</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>補正しない</t>
         </is>
@@ -6570,7 +6570,7 @@
           <t>年平均の差が0.2ポイント以上0.5ポイント未満</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>補正する（係数を明示）</t>
         </is>
@@ -6597,7 +6597,7 @@
           <t>年平均の差が0.5ポイント以上</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>補正したうえで、伸び率の置き方そのものを再検討</t>
         </is>
@@ -6624,7 +6624,7 @@
           <t>町ごとに差の向きが異なる場合</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>町別に係数を分ける</t>
         </is>
@@ -6651,7 +6651,7 @@
           <t>社人研推計の基準年から推計年までの区間が取れる場合</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>その区間を優先する</t>
         </is>
@@ -6678,7 +6678,7 @@
           <t>総人口の目標値</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>伸び率の補正には用いない</t>
         </is>
@@ -6692,7 +6692,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>【2　本表への指摘（レッドチーム方式）】</t>
+          <t>【2　本表への指摘（自己点検方式）】</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>重大</t>
         </is>
@@ -6838,7 +6838,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>重大</t>
         </is>

--- a/output/第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx
+++ b/output/第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>75歳以上は、東川町が上方（3年で+3.2％）、美瑛町が補正しない、東神楽町が下方（4.2％）である。65〜74歳は、東川町が補正しない、美瑛町が上方（+6.2％）、東神楽町が上方（+4.2％）である。3町計で75歳以上に下方補正が生じる原因は、実質的に東神楽町にある。町別の補正係数は算定したが、適用には町別の基準人口（第1号被保険者数・年齢階級別・令和8年3月末）を要するため保留とする。</t>
+          <t>75歳以上は、東川町が上方（3年で-0.4％）、美瑛町が補正しない、東神楽町が下方（2.2％）である。65〜74歳は、東川町が補正しない、美瑛町が上方（+3.6％）、東神楽町が上方（+2.3％）である。3町計で75歳以上に下方補正が生じる原因は、実質的に東神楽町にある。町別の補正係数は算定したが、適用には町別の基準人口（第1号被保険者数・年齢階級別・令和8年3月末）を要するため保留とする。</t>
         </is>
       </c>
     </row>
@@ -2746,27 +2746,27 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>1,270人</t>
+          <t>1,269人</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>1,070人</t>
+          <t>972人</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>-3.37％</t>
+          <t>-5.19％</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>-0.13pt</t>
-        </is>
-      </c>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t>補正しない（3年で+0.4％）</t>
+          <t>-1.96pt</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>上方に補正（3年で+6.3％）</t>
         </is>
       </c>
     </row>
@@ -2799,22 +2799,22 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>1,632人</t>
+          <t>1,731人</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>+1.83％</t>
+          <t>+3.04％</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>-1.08pt</t>
-        </is>
-      </c>
-      <c r="J7" s="20" t="inlineStr">
-        <is>
-          <t>上方に補正（3年で+3.2％）</t>
+          <t>+0.13pt</t>
+        </is>
+      </c>
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t>補正しない（3年で-0.4％）</t>
         </is>
       </c>
     </row>
@@ -2842,22 +2842,22 @@
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>2,760人</t>
+          <t>2,759人</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
         <is>
-          <t>2,702人</t>
+          <t>2,703人</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
         <is>
-          <t>-0.43％</t>
+          <t>-0.41％</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
         <is>
-          <t>-0.61pt</t>
+          <t>-0.59pt</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -2894,27 +2894,27 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>1,617人</t>
+          <t>1,616人</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>1,274人</t>
+          <t>1,327人</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>-4.66％</t>
+          <t>-3.86％</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>-1.94pt</t>
+          <t>-1.15pt</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
         <is>
-          <t>上方に補正（3年で+6.2％）</t>
+          <t>上方に補正（3年で+3.6％）</t>
         </is>
       </c>
     </row>
@@ -2942,27 +2942,27 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>2,134人</t>
+          <t>2,133人</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>2,230人</t>
+          <t>2,176人</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>+0.88％</t>
+          <t>+0.40％</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>+0.20pt</t>
-        </is>
-      </c>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t>補正しない（3年で-0.6％）</t>
+          <t>-0.29pt</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>上方に補正（3年で+0.9％）</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
-          <t>3,751人</t>
+          <t>3,749人</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t>3,504人</t>
+          <t>3,503人</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t>上方に補正（3年で+2.0％）</t>
+          <t>上方に補正（3年で+1.9％）</t>
         </is>
       </c>
     </row>
@@ -3042,27 +3042,27 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>1,384人</t>
+          <t>1,387人</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>1,280人</t>
+          <t>1,323人</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>-1.55％</t>
+          <t>-0.94％</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>-1.36pt</t>
+          <t>-0.75pt</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
         <is>
-          <t>上方に補正（3年で+4.2％）</t>
+          <t>上方に補正（3年で+2.3％）</t>
         </is>
       </c>
     </row>
@@ -3090,27 +3090,27 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>1,543人</t>
+          <t>1,557人</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>1,839人</t>
+          <t>1,794人</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>+3.58％</t>
+          <t>+2.87％</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>+1.48pt</t>
+          <t>+0.78pt</t>
         </is>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>下方に補正（3年で-4.2％）</t>
+          <t>下方に補正（3年で-2.2％）</t>
         </is>
       </c>
     </row>
@@ -3138,27 +3138,27 @@
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t>2,927人</t>
+          <t>2,944人</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
         <is>
-          <t>3,119人</t>
+          <t>3,117人</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
         <is>
-          <t>+1.28％</t>
+          <t>+1.15％</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
         <is>
-          <t>+0.28pt</t>
+          <t>+0.15pt</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t>下方に補正（3年で-0.8％）</t>
+          <t>補正しない（3年で-0.4％）</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>注1）「65歳以上」の行は「65〜74歳」と「75歳以上」の合計であり、内訳の2区分と重複するため網掛けとした。補正は内訳の2区分に対して行う。注2）補正方向は、年平均の差が±0.20ポイント未満のときは「補正しない」、社人研が速いときは「下方に補正」、住民基本台帳が速いときは「上方に補正」とした（07シートの判定ルール）。美瑛町の75歳以上は差が0.195ポイントで、判定の境界にある。表示は四捨五入して+0.20ポイントとなるが、しきい値0.20ポイントを下回るため「補正しない」とした［要確認］。注3）「3年で〇％」は、令和8年度を起点に令和11年度までの3年に年平均の差を当てはめた累積である。</t>
+          <t>注1）「65歳以上」の行は「65〜74歳」と「75歳以上」の合計であり、内訳の2区分と重複するため網掛けとした。補正は内訳の2区分に対して行う。注2）補正方向は、年平均の差が±0.20ポイント未満のときは「補正しない」、社人研が速いときは「下方に補正」、住民基本台帳が速いときは「上方に補正」とした（07シートの判定ルール）。美瑛町の75歳以上は差が0.288ポイントで、判定の境界にある。表示は四捨五入して-0.29ポイントとなるが、しきい値0.20ポイントを下回るため「補正しない」とした［要確認］。注3）「3年で〇％」は、令和8年度を起点に令和11年度までの3年に年平均の差を当てはめた累積である。</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>65〜74歳は社人研とほぼ一致する（差-0.13ポイント）。75歳以上は住民基本台帳の方が速く（差-1.08ポイント）、3年で+3.2％の上方補正となる。3町で唯一、75歳以上を上方に補正する町である。</t>
+          <t>65〜74歳は社人研の減少見込みが実績より速く（差-1.96ポイント）、3年で+6.3％の上方補正となる。3町で最も大きい前期高齢者の補正である。75歳以上は差が+0.13ポイントで補正しない。</t>
         </is>
       </c>
       <c r="C22" s="14" t="n"/>
@@ -3368,7 +3368,7 @@
       <c r="I22" s="15" t="n"/>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>総人口が令和2年から令和7年にかけて8,380人から8,673人へ293人増えた3町で唯一の町である。社人研は同期間に減少を見込んでいた。移住施策による転入が75歳以上の増加を上回る速度で総人口を押し上げている一方、75歳以上そのものも実績の方が速く増えている</t>
+          <t>総人口が令和2年から令和7年にかけて8,380人から8,673人へ293人増えた3町で唯一の町である。社人研は同期間に減少を見込んでいた。75歳以上は社人研の令和7年1,731人に対し実績1,637人で、水準は社人研の方が高いが伸び率はほぼ同じである</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>65〜74歳は社人研の減少見込みが実績より大幅に速く（差-1.94ポイント）、3年で+6.2％の上方補正となる。75歳以上は差が+0.20ポイントで補正しない。</t>
+          <t>65〜74歳は社人研の減少見込みが実績より速く（差-1.15ポイント）、3年で+3.6％の上方補正となる。75歳以上も社人研の方が緩やかで（差-0.29ポイント）、3年で+0.9％の上方補正となる。3町で唯一、両区分とも上方に補正する町である。</t>
         </is>
       </c>
       <c r="C23" s="14" t="n"/>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>65〜74歳は3年で+4.2％の上方補正、75歳以上は社人研が年+1.48ポイント速く、3年で4.2％の下方補正となる。3町で唯一、75歳以上を下方に補正する町である。</t>
+          <t>65〜74歳は3年で+2.3％の上方補正、75歳以上は社人研が年+0.78ポイント速く、3年で2.2％の下方補正となる。3町で唯一、75歳以上を下方に補正する町である。</t>
         </is>
       </c>
       <c r="C24" s="14" t="n"/>
@@ -3416,7 +3416,7 @@
       <c r="I24" s="15" t="n"/>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>3町計で75歳以上に下方補正が生じる原因は、実質的にこの町にある。社人研は令和7年の75歳以上を1,839人と見込んでいたが、実績は1,552人で287人少ない。旭川市に隣接し人口構成が若い町で、後期高齢化の速度が推計より緩やかである</t>
+          <t>3町計で75歳以上に下方補正が生じる原因は、実質的にこの町にある。社人研は令和7年の75歳以上を1,794人と見込んでいたが、実績は1,552人で242人少ない。旭川市に隣接し人口構成が若い町で、後期高齢化の速度が推計より緩やかである</t>
         </is>
       </c>
     </row>
@@ -3491,13 +3491,13 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>1.0632</t>
         </is>
       </c>
       <c r="C29" s="15" t="n"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>1.0322</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="E29" s="15" t="n"/>
@@ -3511,7 +3511,7 @@
       <c r="I29" s="15" t="n"/>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>社人研側の町別75歳以上は当方の按分値である。町別の公表値ではない</t>
+          <t>社人研側の町別75歳以上は結果表3-4の公表値による（令和8年8月31日受領）</t>
         </is>
       </c>
     </row>
@@ -3523,13 +3523,13 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>1.0624</t>
+          <t>1.0362</t>
         </is>
       </c>
       <c r="C30" s="15" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>1.0086</t>
         </is>
       </c>
       <c r="E30" s="15" t="n"/>
@@ -3543,7 +3543,7 @@
       <c r="I30" s="15" t="n"/>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>社人研側の町別75歳以上は当方の按分値である。町別の公表値ではない</t>
+          <t>社人研側の町別75歳以上は結果表3-4の公表値による（令和8年8月31日受領）</t>
         </is>
       </c>
     </row>
@@ -3555,13 +3555,13 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>1.0420</t>
+          <t>1.0228</t>
         </is>
       </c>
       <c r="C31" s="15" t="n"/>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>0.9578</t>
+          <t>0.9775</t>
         </is>
       </c>
       <c r="E31" s="15" t="n"/>
@@ -3575,7 +3575,7 @@
       <c r="I31" s="15" t="n"/>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>社人研側の町別75歳以上は当方の按分値である。町別の公表値ではない</t>
+          <t>社人研側の町別75歳以上は結果表3-4の公表値による（令和8年8月31日受領）</t>
         </is>
       </c>
     </row>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="65" customHeight="1">
+    <row r="33" ht="78" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>注1）町別の補正係数は算定したが、適用は保留する。当方の推計は基準人口（第1号被保険者数）に伸び率を掛ける構造であるため、町別に適用するには町別の基準人口（65〜74歳・75〜84歳・85歳以上の第1号被保険者数、令和8年3月末）が必要である。現在は3町計のみを見える化B4cから得ている。注2）社人研側の町別75歳以上は、令和2年国勢調査の町別75歳以上を起点に3町計の後期高齢者比の推移で按分した値である。町ごとに後期化の速度が異なる場合は誤差が生じる。町別65歳以上は見える化A1の町別総人口×町別高齢化率であり、按分ではない。したがって、65〜74歳と75歳以上の切り分けには按分の仮定が入っている点に留意を要する［要確認］。注3）補正を町別に適用しない場合でも、サービス見込量の町別配分や施設整備の判断では、東川町と東神楽町で75歳以上の伸びの向きが逆であることを踏まえる必要がある。</t>
+          <t>注1）町別の補正係数は算定したが、適用は保留する。当方の推計は基準人口（第1号被保険者数）に伸び率を掛ける構造であるため、町別に適用するには町別の基準人口（65〜74歳・75〜84歳・85歳以上の第1号被保険者数、令和8年3月末）が必要である。現在は3町計のみを見える化B4cから得ている。注2）社人研側の町別65歳以上・75歳以上は、社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-3・3-4の町別の年齢別人口割合（公表値）に町別総人口を乗じて求めた（令和8年8月31日受領）。令和8年8月30日までは、令和2年国勢調査の町別75歳以上を起点に3町計の後期高齢者比の推移で按分していた。按分値との差は最大で122人（東川町・令和12年）であり、町別の補正方向が4件変わった。3町計の値と補正係数は変わっていない。注3）補正を町別に適用しない場合でも、サービス見込量の町別配分や施設整備の判断では、東川町と東神楽町で75歳以上の伸びの向きが逆であることを踏まえる必要がある。</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>3年で1.5％以上の差。3町計の65〜74歳（年1.20ポイント）と東神楽町の75歳以上（年1.48ポイント）はここに当たる</t>
+          <t>3年で1.5％以上の差。3町計の65〜74歳（年1.20ポイント）と東神楽町の75歳以上（年0.78ポイント）はここに当たる</t>
         </is>
       </c>
     </row>
@@ -6838,24 +6838,24 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>重大</t>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>解消</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>町別の判定は、社人研側の町別75歳以上が当方の按分値であることに依存している。「東神楽町の75歳以上を下方に補正する」という結論は、按分の仮定が外れれば覆る。</t>
+          <t>町別の判定が、社人研側の町別75歳以上を当方の按分値に依存していた点は、令和8年8月31日の受領により解消した。</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>住民基本台帳側は原表の受領により按分が不要になったが、社人研側は依然として按分値である。令和2年の75歳以上/65歳以上比は東川町54.0％・美瑛町56.9％・東神楽町52.7％と差があり、この比が将来も同じ倍率で動くと仮定している。東神楽町の75歳以上の社人研値1,839人（令和7年）はこの仮定の産物である。</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-3・3-4の町別の年齢別人口割合を受領し、按分をやめて公表値に置き換えた。按分値との差は最大122人（東川町・令和12年）で、町別の補正方向が4件変わった。東川町の75歳以上は「上方に補正」から「補正しない」へ、美瑛町の75歳以上は「補正しない」から「上方に補正」へ、東川町の65〜74歳は「補正しない」から「上方に補正」へ、東神楽町の65歳以上は「下方に補正」から「補正しない」へ変わった。</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」の男女5歳階級別の市区町村別表（東川町01458・美瑛町01459・東神楽町01453）を直接取得すれば、按分は不要になる。取得までは町別の75歳以上の判定は暫定とする</t>
+          <t>3町計の値と補正係数（65〜74歳1.0377・75歳以上0.9927）は変わっていない。保険料への影響もない。町別の判定は公表値に基づくものとなった</t>
         </is>
       </c>
     </row>
@@ -6940,10 +6940,10 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="78" customHeight="1">
+    <row r="25" ht="65" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>注1）指摘No.1・No.2は、本表の結論（水準の補正は不要、75歳以上の伸び率のみ補正）そのものを揺るがすものである。いずれも反証条件が示されており、住所地特例の適用者数と、国勢調査・住民基本台帳の差の推移が得られれば決着する。注2）指摘No.3（適用年数のずれ）は、補正係数の算定方法に関わる。3年か4年かで補正の大きさが変わるため、計画本文に用いる前に決定する。注3）指摘No.6のとおり、比較期間の選び方で判定が変わる。案Bを採る理由は判定ルール⑦に置いた。注4）指摘No.5は、町別のデータの受領により住民基本台帳側の按分が不要になった一方で、社人研側が按分値のまま残ったため、「中」から「重大」に引き上げた。町別の75歳以上の補正方向は、社人研の市区町村別・男女5歳階級別表の取得までは暫定である。注5）指摘No.7の反証条件（令和8年1月1日の町別内訳）は、05シートの【4】④として資料提供を依頼する。</t>
+          <t>注1）指摘No.1・No.2は、本表の結論（水準の補正は不要、75歳以上の伸び率のみ補正）そのものを揺るがすものである。いずれも反証条件が示されており、住所地特例の適用者数と、国勢調査・住民基本台帳の差の推移が得られれば決着する。注2）指摘No.3（適用年数のずれ）は、補正係数の算定方法に関わる。3年か4年かで補正の大きさが変わるため、計画本文に用いる前に決定する。注3）指摘No.6のとおり、比較期間の選び方で判定が変わる。案Bを採る理由は判定ルール⑦に置いた。注4）指摘No.5は、令和8年8月31日に社人研の結果表3-3・3-4を受領し、按分をやめて公表値に置き換えたことにより解消した。町別の補正方向は公表値に基づくものとなった。注5）指摘No.7の反証条件（令和8年1月1日の町別内訳）は、05シートの【4】④として資料提供を依頼する。</t>
         </is>
       </c>
     </row>
